--- a/pipeline/sources/NLR2026_Eng.xlsx
+++ b/pipeline/sources/NLR2026_Eng.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hkexgroup.sharepoint.com/sites/IPOV/L/IPO Reports/IPO New Listing Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="13_ncr:1_{CC06123C-E2C8-4CAD-95FD-FBB98F855C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAEC20F7-8DE2-414D-8317-6E1B7DA5F2AB}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{4B032253-3393-4BC9-A00B-E799DD85AB89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B14EEF41-D31F-4B91-AA32-985DC51DA96D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="654" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="654" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NLR" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="365">
   <si>
     <t>Stock Code</t>
   </si>
@@ -1222,9 +1222,6 @@
 Citigroup Global Markets Asia Limited</t>
   </si>
   <si>
-    <t xml:space="preserve">Year 2026 (up to 9 September 2026) </t>
-  </si>
-  <si>
     <t>03231</t>
   </si>
   <si>
@@ -1232,6 +1229,44 @@
   </si>
   <si>
     <t>Silver Nile Global Investments Limited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year 2026 (up to 29 September 2026) </t>
+  </si>
+  <si>
+    <t>Ligent Technologies, Inc.</t>
+  </si>
+  <si>
+    <t>Citigroup Global Markets Asia Limited / 
+CITIC Securities (Hong Kong) Limited</t>
+  </si>
+  <si>
+    <t>Red Avenue New Materials Group Co., Ltd.</t>
+  </si>
+  <si>
+    <t>Transwarp Technology (Shanghai) Co., Ltd - H Shares</t>
+  </si>
+  <si>
+    <t>Grant Thornton Hong Kong Limited</t>
+  </si>
+  <si>
+    <t>Huatai Financial Holdings (Hong Kong) Limited/
+Citigroup Global Markets Asia Limited/
+Orient Capital (Hong Kong) Limited</t>
+  </si>
+  <si>
+    <t>Direct Drive Tech Limited - H Shares</t>
+  </si>
+  <si>
+    <t>RoboTechnik Intelligent Technology Co., Ltd.  - H Shares</t>
+  </si>
+  <si>
+    <t>Shenzhen Kinwong Electronic Co., Ltd. - H Shares</t>
+  </si>
+  <si>
+    <t>CITIC Securities (Hong Kong) Limited / 
+Merrill Lynch (Asia Pacific) Limited / 
+Guolian Securities International Capital Market Co., Limited</t>
   </si>
 </sst>
 </file>
@@ -1400,7 +1435,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1450,9 +1485,6 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1460,9 +1492,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1498,6 +1527,18 @@
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="39">
@@ -1842,26 +1883,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:O225"/>
+  <dimension ref="A1:O242"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.625" style="13" customWidth="1"/>
-    <col min="2" max="2" width="8.875" style="24" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="22" customWidth="1"/>
     <col min="3" max="3" width="49.875" style="14" customWidth="1"/>
-    <col min="4" max="4" width="12.625" style="18" customWidth="1"/>
-    <col min="5" max="5" width="13.75" style="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="49.25" style="19" customWidth="1"/>
-    <col min="7" max="7" width="27.375" style="19" customWidth="1"/>
-    <col min="8" max="8" width="22.375" style="19" customWidth="1"/>
-    <col min="9" max="9" width="18.5" style="20" customWidth="1"/>
-    <col min="10" max="10" width="18.375" style="21" customWidth="1"/>
+    <col min="4" max="4" width="12.625" style="17" customWidth="1"/>
+    <col min="5" max="5" width="13.75" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="56.125" style="18" customWidth="1"/>
+    <col min="7" max="7" width="27.375" style="18" customWidth="1"/>
+    <col min="8" max="8" width="22.375" style="18" customWidth="1"/>
+    <col min="9" max="9" width="18.5" style="19" customWidth="1"/>
+    <col min="10" max="10" width="18.375" style="35" customWidth="1"/>
     <col min="11" max="11" width="4.125" style="4" customWidth="1"/>
     <col min="12" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
-        <v>351</v>
+      <c r="A1" s="20" t="s">
+        <v>354</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="1"/>
@@ -1871,7 +1912,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="16"/>
-      <c r="J1" s="1"/>
+      <c r="J1" s="32"/>
     </row>
     <row r="2" spans="1:11" s="12" customFormat="1" ht="48" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
@@ -1899,7 +1940,7 @@
       <c r="I2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="33" t="s">
         <v>8</v>
       </c>
       <c r="K2" s="11"/>
@@ -1908,16 +1949,16 @@
       <c r="A3" s="13">
         <v>1</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="25" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D3" s="23">
         <v>46013</v>
       </c>
-      <c r="E3" s="25">
+      <c r="E3" s="23">
         <v>46024</v>
       </c>
       <c r="F3" s="15" t="s">
@@ -1932,24 +1973,24 @@
       <c r="I3" s="16">
         <v>970956560.00000012</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="34">
         <v>19.600000000000001</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K3" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="25" t="s">
+      <c r="B4" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="15" t="s">
@@ -1964,10 +2005,10 @@
       <c r="I4" s="16">
         <v>5449482080</v>
       </c>
-      <c r="J4" s="17">
+      <c r="J4" s="34">
         <v>19.600000000000001</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="K4" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1975,16 +2016,16 @@
       <c r="A5" s="13">
         <v>2</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="25" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="23">
         <v>46021</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="23">
         <v>46030</v>
       </c>
       <c r="F5" s="15" t="s">
@@ -1993,30 +2034,30 @@
       <c r="G5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="25" t="s">
+      <c r="H5" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I5" s="16">
         <v>869629180</v>
       </c>
-      <c r="J5" s="17">
+      <c r="J5" s="34">
         <v>116.2</v>
       </c>
-      <c r="K5" s="26" t="s">
+      <c r="K5" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B6" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="25" t="s">
+      <c r="B6" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="15" t="s">
@@ -2031,10 +2072,10 @@
       <c r="I6" s="16">
         <v>4130735700</v>
       </c>
-      <c r="J6" s="17">
+      <c r="J6" s="34">
         <v>116.2</v>
       </c>
-      <c r="K6" s="26" t="s">
+      <c r="K6" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2042,16 +2083,16 @@
       <c r="A7" s="13">
         <v>3</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="25" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="23">
         <v>46021</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="23">
         <v>46030</v>
       </c>
       <c r="F7" s="15" t="s">
@@ -2060,30 +2101,30 @@
       <c r="G7" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="H7" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I7" s="16">
         <v>367746720</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="34">
         <v>144.6</v>
       </c>
-      <c r="K7" s="26" t="s">
+      <c r="K7" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B8" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="25" t="s">
+      <c r="B8" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="15" t="s">
@@ -2098,10 +2139,10 @@
       <c r="I8" s="16">
         <v>3309691560</v>
       </c>
-      <c r="J8" s="17">
+      <c r="J8" s="34">
         <v>144.6</v>
       </c>
-      <c r="K8" s="26" t="s">
+      <c r="K8" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2109,16 +2150,16 @@
       <c r="A9" s="13">
         <v>4</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="25" t="s">
         <v>26</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="23">
         <v>46021</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="23">
         <v>46030</v>
       </c>
       <c r="F9" s="15" t="s">
@@ -2127,30 +2168,30 @@
       <c r="G9" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="25" t="s">
+      <c r="H9" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I9" s="16">
         <v>119874252</v>
       </c>
-      <c r="J9" s="17">
+      <c r="J9" s="34">
         <v>43.24</v>
       </c>
-      <c r="K9" s="26" t="s">
+      <c r="K9" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B10" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="25" t="s">
+      <c r="B10" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="15" t="s">
@@ -2165,10 +2206,10 @@
       <c r="I10" s="16">
         <v>1258638568</v>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="34">
         <v>43.24</v>
       </c>
-      <c r="K10" s="26" t="s">
+      <c r="K10" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2176,16 +2217,16 @@
       <c r="A11" s="13">
         <v>5</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="25" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="23">
         <v>46022</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="23">
         <v>46031</v>
       </c>
       <c r="F11" s="15" t="s">
@@ -2194,30 +2235,30 @@
       <c r="G11" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="25" t="s">
+      <c r="H11" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I11" s="16">
         <v>837846900</v>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="34">
         <v>165</v>
       </c>
-      <c r="K11" s="26" t="s">
+      <c r="K11" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B12" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="25" t="s">
+      <c r="B12" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F12" s="15" t="s">
@@ -2232,10 +2273,10 @@
       <c r="I12" s="16">
         <v>4702397700</v>
       </c>
-      <c r="J12" s="17">
+      <c r="J12" s="34">
         <v>165</v>
       </c>
-      <c r="K12" s="26" t="s">
+      <c r="K12" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2243,16 +2284,16 @@
       <c r="A13" s="13">
         <v>6</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="25" t="s">
         <v>32</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="23">
         <v>46022</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="23">
         <v>46031</v>
       </c>
       <c r="F13" s="15" t="s">
@@ -2261,30 +2302,30 @@
       <c r="G13" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="25" t="s">
+      <c r="H13" s="23" t="s">
         <v>35</v>
       </c>
       <c r="I13" s="16">
         <v>159347936</v>
       </c>
-      <c r="J13" s="17">
+      <c r="J13" s="34">
         <v>57.97</v>
       </c>
-      <c r="K13" s="26" t="s">
+      <c r="K13" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B14" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="25" t="s">
+      <c r="B14" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F14" s="15" t="s">
@@ -2299,10 +2340,10 @@
       <c r="I14" s="16">
         <v>1947965910</v>
       </c>
-      <c r="J14" s="17">
+      <c r="J14" s="34">
         <v>57.97</v>
       </c>
-      <c r="K14" s="26" t="s">
+      <c r="K14" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2310,16 +2351,16 @@
       <c r="A15" s="13">
         <v>7</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="25" t="s">
         <v>36</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="23">
         <v>46022</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="23">
         <v>46031</v>
       </c>
       <c r="F15" s="15" t="s">
@@ -2328,30 +2369,30 @@
       <c r="G15" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="25" t="s">
+      <c r="H15" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I15" s="16">
         <v>110298000</v>
       </c>
-      <c r="J15" s="17">
+      <c r="J15" s="34">
         <v>30</v>
       </c>
-      <c r="K15" s="26" t="s">
+      <c r="K15" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B16" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="25" t="s">
+      <c r="B16" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F16" s="15" t="s">
@@ -2366,10 +2407,10 @@
       <c r="I16" s="16">
         <v>1158114000</v>
       </c>
-      <c r="J16" s="17">
+      <c r="J16" s="34">
         <v>30</v>
       </c>
-      <c r="K16" s="26" t="s">
+      <c r="K16" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2377,16 +2418,16 @@
       <c r="A17" s="13">
         <v>8</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="25" t="s">
         <v>39</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="23">
         <v>46022</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="23">
         <v>46034</v>
       </c>
       <c r="F17" s="15" t="s">
@@ -2395,33 +2436,33 @@
       <c r="G17" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="H17" s="25" t="s">
+      <c r="H17" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I17" s="16">
         <v>479984000</v>
       </c>
-      <c r="J17" s="17">
+      <c r="J17" s="34">
         <v>104.8</v>
       </c>
-      <c r="K17" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L17" s="28"/>
+      <c r="K17" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L17" s="26"/>
       <c r="M17"/>
-      <c r="N17" s="29"/>
+      <c r="N17" s="27"/>
     </row>
     <row r="18" spans="1:14" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" s="25" t="s">
+      <c r="B18" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F18" s="15" t="s">
@@ -2436,30 +2477,30 @@
       <c r="I18" s="16">
         <v>4837683280</v>
       </c>
-      <c r="J18" s="17">
+      <c r="J18" s="34">
         <v>104.8</v>
       </c>
-      <c r="K18" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="L18" s="28"/>
+      <c r="K18" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="L18" s="26"/>
       <c r="M18"/>
-      <c r="N18" s="29"/>
+      <c r="N18" s="27"/>
     </row>
     <row r="19" spans="1:14" ht="75" x14ac:dyDescent="0.2">
       <c r="A19" s="13">
         <v>9</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="25" t="s">
         <v>43</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="23">
         <v>46022</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="23">
         <v>46035</v>
       </c>
       <c r="F19" s="15" t="s">
@@ -2468,30 +2509,30 @@
       <c r="G19" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="25" t="s">
+      <c r="H19" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I19" s="16">
         <v>468439200</v>
       </c>
-      <c r="J19" s="17">
+      <c r="J19" s="34">
         <v>162</v>
       </c>
-      <c r="K19" s="26" t="s">
+      <c r="K19" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="25" t="s">
+      <c r="B20" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F20" s="15" t="s">
@@ -2506,10 +2547,10 @@
       <c r="I20" s="16">
         <v>4918563000</v>
       </c>
-      <c r="J20" s="17">
+      <c r="J20" s="34">
         <v>162</v>
       </c>
-      <c r="K20" s="26" t="s">
+      <c r="K20" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2517,16 +2558,16 @@
       <c r="A21" s="13">
         <v>10</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="25" t="s">
         <v>46</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="23">
         <v>46022</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="23">
         <v>46035</v>
       </c>
       <c r="F21" s="15" t="s">
@@ -2541,24 +2582,24 @@
       <c r="I21" s="16">
         <v>28522890</v>
       </c>
-      <c r="J21" s="17">
+      <c r="J21" s="34">
         <v>12.26</v>
       </c>
-      <c r="K21" s="26" t="s">
+      <c r="K21" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B22" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" s="25" t="s">
+      <c r="B22" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="15" t="s">
@@ -2573,10 +2614,10 @@
       <c r="I22" s="16">
         <v>256681490</v>
       </c>
-      <c r="J22" s="17">
+      <c r="J22" s="34">
         <v>12.26</v>
       </c>
-      <c r="K22" s="26" t="s">
+      <c r="K22" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2584,16 +2625,16 @@
       <c r="A23" s="13">
         <v>11</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="25" t="s">
         <v>50</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="25">
+      <c r="D23" s="23">
         <v>46036</v>
       </c>
-      <c r="E23" s="25">
+      <c r="E23" s="23">
         <v>46044</v>
       </c>
       <c r="F23" s="15" t="s">
@@ -2602,30 +2643,30 @@
       <c r="G23" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H23" s="25" t="s">
+      <c r="H23" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I23" s="16">
         <v>162006000</v>
       </c>
-      <c r="J23" s="17">
+      <c r="J23" s="34">
         <v>31</v>
       </c>
-      <c r="K23" s="26" t="s">
+      <c r="K23" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B24" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" s="25" t="s">
+      <c r="B24" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F24" s="15" t="s">
@@ -2640,10 +2681,10 @@
       <c r="I24" s="16">
         <v>1458026100</v>
       </c>
-      <c r="J24" s="17">
+      <c r="J24" s="34">
         <v>31</v>
       </c>
-      <c r="K24" s="26" t="s">
+      <c r="K24" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2651,16 +2692,16 @@
       <c r="A25" s="13">
         <v>12</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="25" t="s">
         <v>53</v>
       </c>
       <c r="C25" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D25" s="25">
+      <c r="D25" s="23">
         <v>46042</v>
       </c>
-      <c r="E25" s="25">
+      <c r="E25" s="23">
         <v>46050</v>
       </c>
       <c r="F25" s="15" t="s">
@@ -2669,32 +2710,32 @@
       <c r="G25" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="H25" s="25" t="s">
+      <c r="H25" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I25" s="16">
         <v>333653320</v>
       </c>
-      <c r="J25" s="17">
+      <c r="J25" s="34">
         <v>236.6</v>
       </c>
-      <c r="K25" s="26" t="s">
+      <c r="K25" s="24" t="s">
         <v>14</v>
       </c>
       <c r="M25"/>
-      <c r="N25" s="29"/>
+      <c r="N25" s="27"/>
     </row>
     <row r="26" spans="1:14" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="25" t="s">
+      <c r="B26" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="15" t="s">
@@ -2709,30 +2750,30 @@
       <c r="I26" s="16">
         <v>3886770160</v>
       </c>
-      <c r="J26" s="17">
+      <c r="J26" s="34">
         <v>236.6</v>
       </c>
-      <c r="K26" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="L26" s="28"/>
+      <c r="K26" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="L26" s="26"/>
       <c r="M26"/>
-      <c r="N26" s="29"/>
+      <c r="N26" s="27"/>
     </row>
     <row r="27" spans="1:14" s="13" customFormat="1" ht="60" x14ac:dyDescent="0.2">
       <c r="A27" s="13">
         <v>13</v>
       </c>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="25" t="s">
         <v>57</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D27" s="25">
+      <c r="D27" s="23">
         <v>46048</v>
       </c>
-      <c r="E27" s="25">
+      <c r="E27" s="23">
         <v>46056</v>
       </c>
       <c r="F27" s="15" t="s">
@@ -2741,33 +2782,33 @@
       <c r="G27" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="H27" s="25" t="s">
+      <c r="H27" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I27" s="16">
         <v>1014072000</v>
       </c>
-      <c r="J27" s="17">
+      <c r="J27" s="34">
         <v>248</v>
       </c>
-      <c r="K27" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L27" s="28"/>
+      <c r="K27" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L27" s="26"/>
       <c r="M27"/>
-      <c r="N27" s="29"/>
+      <c r="N27" s="27"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B28" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="25" t="s">
+      <c r="B28" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="15" t="s">
@@ -2782,10 +2823,10 @@
       <c r="I28" s="16">
         <v>10085341600</v>
       </c>
-      <c r="J28" s="17">
+      <c r="J28" s="34">
         <v>248</v>
       </c>
-      <c r="K28" s="26" t="s">
+      <c r="K28" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2793,16 +2834,16 @@
       <c r="A29" s="13">
         <v>14</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="25" t="s">
         <v>61</v>
       </c>
       <c r="C29" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="25">
+      <c r="D29" s="23">
         <v>46049</v>
       </c>
-      <c r="E29" s="25">
+      <c r="E29" s="23">
         <v>46057</v>
       </c>
       <c r="F29" s="15" t="s">
@@ -2811,33 +2852,33 @@
       <c r="G29" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="H29" s="25" t="s">
+      <c r="H29" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I29" s="16">
         <v>108000000</v>
       </c>
-      <c r="J29" s="17">
+      <c r="J29" s="34">
         <v>36</v>
       </c>
-      <c r="K29" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L29" s="28"/>
+      <c r="K29" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L29" s="26"/>
       <c r="M29"/>
-      <c r="N29" s="29"/>
+      <c r="N29" s="27"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B30" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" s="25" t="s">
+      <c r="B30" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="15" t="s">
@@ -2852,10 +2893,10 @@
       <c r="I30" s="16">
         <v>972000000</v>
       </c>
-      <c r="J30" s="17">
+      <c r="J30" s="34">
         <v>36</v>
       </c>
-      <c r="K30" s="26" t="s">
+      <c r="K30" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2863,16 +2904,16 @@
       <c r="A31" s="13">
         <v>15</v>
       </c>
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="25" t="s">
         <v>65</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="D31" s="25">
+      <c r="D31" s="23">
         <v>46051</v>
       </c>
-      <c r="E31" s="25">
+      <c r="E31" s="23">
         <v>46059</v>
       </c>
       <c r="F31" s="15" t="s">
@@ -2881,33 +2922,33 @@
       <c r="G31" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="H31" s="25" t="s">
+      <c r="H31" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I31" s="16">
         <v>28452500</v>
       </c>
-      <c r="J31" s="17">
+      <c r="J31" s="34">
         <v>59.9</v>
       </c>
-      <c r="K31" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L31" s="28"/>
+      <c r="K31" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L31" s="26"/>
       <c r="M31"/>
-      <c r="N31" s="29"/>
+      <c r="N31" s="27"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B32" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" s="25" t="s">
+      <c r="B32" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F32" s="15" t="s">
@@ -2922,10 +2963,10 @@
       <c r="I32" s="16">
         <v>267818890</v>
       </c>
-      <c r="J32" s="17">
+      <c r="J32" s="34">
         <v>59.9</v>
       </c>
-      <c r="K32" s="26" t="s">
+      <c r="K32" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2933,16 +2974,16 @@
       <c r="A33" s="13">
         <v>16</v>
       </c>
-      <c r="B33" s="27" t="s">
+      <c r="B33" s="25" t="s">
         <v>68</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="D33" s="25">
+      <c r="D33" s="23">
         <v>46051</v>
       </c>
-      <c r="E33" s="25">
+      <c r="E33" s="23">
         <v>46059</v>
       </c>
       <c r="F33" s="15" t="s">
@@ -2951,33 +2992,33 @@
       <c r="G33" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="H33" s="25" t="s">
+      <c r="H33" s="23" t="s">
         <v>72</v>
       </c>
       <c r="I33" s="16">
         <v>1068412800</v>
       </c>
-      <c r="J33" s="17">
+      <c r="J33" s="34">
         <v>39</v>
       </c>
-      <c r="K33" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L33" s="28"/>
+      <c r="K33" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L33" s="26"/>
       <c r="M33"/>
-      <c r="N33" s="29"/>
+      <c r="N33" s="27"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B34" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C34" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" s="25" t="s">
+      <c r="B34" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F34" s="15" t="s">
@@ -2992,10 +3033,10 @@
       <c r="I34" s="16">
         <v>11030288100</v>
       </c>
-      <c r="J34" s="17">
+      <c r="J34" s="34">
         <v>39</v>
       </c>
-      <c r="K34" s="26" t="s">
+      <c r="K34" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3003,16 +3044,16 @@
       <c r="A35" s="13">
         <v>17</v>
       </c>
-      <c r="B35" s="27" t="s">
+      <c r="B35" s="25" t="s">
         <v>73</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="D35" s="25">
+      <c r="D35" s="23">
         <v>46051</v>
       </c>
-      <c r="E35" s="25">
+      <c r="E35" s="23">
         <v>46059</v>
       </c>
       <c r="F35" s="15" t="s">
@@ -3021,33 +3062,33 @@
       <c r="G35" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H35" s="25" t="s">
+      <c r="H35" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I35" s="16">
         <v>483330160</v>
       </c>
-      <c r="J35" s="17">
+      <c r="J35" s="34">
         <v>95.8</v>
       </c>
-      <c r="K35" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L35" s="28"/>
+      <c r="K35" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L35" s="26"/>
       <c r="M35"/>
-      <c r="N35" s="29"/>
+      <c r="N35" s="27"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B36" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C36" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" s="25" t="s">
+      <c r="B36" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F36" s="15" t="s">
@@ -3062,10 +3103,10 @@
       <c r="I36" s="16">
         <v>5074937940</v>
       </c>
-      <c r="J36" s="17">
+      <c r="J36" s="34">
         <v>95.8</v>
       </c>
-      <c r="K36" s="26" t="s">
+      <c r="K36" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3073,16 +3114,16 @@
       <c r="A37" s="13">
         <v>18</v>
       </c>
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="25" t="s">
         <v>76</v>
       </c>
       <c r="C37" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="D37" s="25">
+      <c r="D37" s="23">
         <v>46052</v>
       </c>
-      <c r="E37" s="25">
+      <c r="E37" s="23">
         <v>46062</v>
       </c>
       <c r="F37" s="15" t="s">
@@ -3091,33 +3132,33 @@
       <c r="G37" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H37" s="25" t="s">
+      <c r="H37" s="23" t="s">
         <v>79</v>
       </c>
       <c r="I37" s="16">
         <v>704298210</v>
       </c>
-      <c r="J37" s="17">
+      <c r="J37" s="34">
         <v>106.89</v>
       </c>
-      <c r="K37" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L37" s="28"/>
+      <c r="K37" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L37" s="26"/>
       <c r="M37"/>
-      <c r="N37" s="29"/>
+      <c r="N37" s="27"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C38" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E38" s="25" t="s">
+      <c r="B38" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F38" s="15" t="s">
@@ -3132,10 +3173,10 @@
       <c r="I38" s="16">
         <v>7395131205</v>
       </c>
-      <c r="J38" s="17">
+      <c r="J38" s="34">
         <v>106.89</v>
       </c>
-      <c r="K38" s="26" t="s">
+      <c r="K38" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3143,16 +3184,16 @@
       <c r="A39" s="13">
         <v>19</v>
       </c>
-      <c r="B39" s="27" t="s">
+      <c r="B39" s="25" t="s">
         <v>80</v>
       </c>
       <c r="C39" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="D39" s="25">
+      <c r="D39" s="23">
         <v>46052</v>
       </c>
-      <c r="E39" s="25">
+      <c r="E39" s="23">
         <v>46063</v>
       </c>
       <c r="F39" s="15" t="s">
@@ -3161,33 +3202,33 @@
       <c r="G39" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H39" s="25" t="s">
+      <c r="H39" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I39" s="16">
         <v>295863120</v>
       </c>
-      <c r="J39" s="17">
+      <c r="J39" s="34">
         <v>28.2</v>
       </c>
-      <c r="K39" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L39" s="28"/>
+      <c r="K39" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L39" s="26"/>
       <c r="M39"/>
-      <c r="N39" s="29"/>
+      <c r="N39" s="27"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B40" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C40" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E40" s="25" t="s">
+      <c r="B40" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F40" s="15" t="s">
@@ -3202,10 +3243,10 @@
       <c r="I40" s="16">
         <v>2695911540</v>
       </c>
-      <c r="J40" s="17">
+      <c r="J40" s="34">
         <v>28.2</v>
       </c>
-      <c r="K40" s="26" t="s">
+      <c r="K40" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3213,16 +3254,16 @@
       <c r="A41" s="13">
         <v>20</v>
       </c>
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="25" t="s">
         <v>83</v>
       </c>
       <c r="C41" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D41" s="25">
+      <c r="D41" s="23">
         <v>46052</v>
       </c>
-      <c r="E41" s="25">
+      <c r="E41" s="23">
         <v>46063</v>
       </c>
       <c r="F41" s="15" t="s">
@@ -3231,33 +3272,33 @@
       <c r="G41" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H41" s="25" t="s">
+      <c r="H41" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I41" s="16">
         <v>34551125</v>
       </c>
-      <c r="J41" s="17">
+      <c r="J41" s="34">
         <v>12.25</v>
       </c>
-      <c r="K41" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L41" s="28"/>
+      <c r="K41" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L41" s="26"/>
       <c r="M41"/>
-      <c r="N41" s="29"/>
+      <c r="N41" s="27"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B42" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E42" s="25" t="s">
+      <c r="B42" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F42" s="15" t="s">
@@ -3272,10 +3313,10 @@
       <c r="I42" s="16">
         <v>310960125</v>
       </c>
-      <c r="J42" s="17">
+      <c r="J42" s="34">
         <v>12.25</v>
       </c>
-      <c r="K42" s="26" t="s">
+      <c r="K42" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3283,16 +3324,16 @@
       <c r="A43" s="13">
         <v>21</v>
       </c>
-      <c r="B43" s="27" t="s">
+      <c r="B43" s="25" t="s">
         <v>85</v>
       </c>
       <c r="C43" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="D43" s="25">
+      <c r="D43" s="23">
         <v>46056</v>
       </c>
-      <c r="E43" s="25">
+      <c r="E43" s="23">
         <v>46064</v>
       </c>
       <c r="F43" s="15" t="s">
@@ -3301,33 +3342,33 @@
       <c r="G43" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="H43" s="25" t="s">
+      <c r="H43" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I43" s="16">
         <v>428761280</v>
       </c>
-      <c r="J43" s="17">
+      <c r="J43" s="34">
         <v>45.8</v>
       </c>
-      <c r="K43" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L43" s="28"/>
+      <c r="K43" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L43" s="26"/>
       <c r="M43"/>
-      <c r="N43" s="29"/>
+      <c r="N43" s="27"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C44" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D44" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E44" s="25" t="s">
+      <c r="B44" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F44" s="15" t="s">
@@ -3342,10 +3383,10 @@
       <c r="I44" s="16">
         <v>4520313440</v>
       </c>
-      <c r="J44" s="17">
+      <c r="J44" s="34">
         <v>45.8</v>
       </c>
-      <c r="K44" s="26" t="s">
+      <c r="K44" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3353,16 +3394,16 @@
       <c r="A45" s="13">
         <v>22</v>
       </c>
-      <c r="B45" s="27" t="s">
+      <c r="B45" s="25" t="s">
         <v>89</v>
       </c>
       <c r="C45" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="D45" s="25">
+      <c r="D45" s="23">
         <v>46058</v>
       </c>
-      <c r="E45" s="25">
+      <c r="E45" s="23">
         <v>46066</v>
       </c>
       <c r="F45" s="15" t="s">
@@ -3371,33 +3412,33 @@
       <c r="G45" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H45" s="25" t="s">
+      <c r="H45" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I45" s="16">
         <v>75854592</v>
       </c>
-      <c r="J45" s="17">
+      <c r="J45" s="34">
         <v>27.06</v>
       </c>
-      <c r="K45" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L45" s="28"/>
+      <c r="K45" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L45" s="26"/>
       <c r="M45"/>
-      <c r="N45" s="29"/>
+      <c r="N45" s="27"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C46" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E46" s="25" t="s">
+      <c r="B46" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F46" s="15" t="s">
@@ -3412,10 +3453,10 @@
       <c r="I46" s="16">
         <v>682642620</v>
       </c>
-      <c r="J46" s="17">
+      <c r="J46" s="34">
         <v>27.06</v>
       </c>
-      <c r="K46" s="26" t="s">
+      <c r="K46" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3423,16 +3464,16 @@
       <c r="A47" s="13">
         <v>23</v>
       </c>
-      <c r="B47" s="27" t="s">
+      <c r="B47" s="25" t="s">
         <v>92</v>
       </c>
       <c r="C47" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="D47" s="25">
+      <c r="D47" s="23">
         <v>46058</v>
       </c>
-      <c r="E47" s="25">
+      <c r="E47" s="23">
         <v>46066</v>
       </c>
       <c r="F47" s="15" t="s">
@@ -3441,33 +3482,33 @@
       <c r="G47" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="H47" s="25" t="s">
+      <c r="H47" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I47" s="16">
         <v>281239910</v>
       </c>
-      <c r="J47" s="17">
+      <c r="J47" s="34">
         <v>20.09</v>
       </c>
-      <c r="K47" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L47" s="28"/>
+      <c r="K47" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L47" s="26"/>
       <c r="M47"/>
-      <c r="N47" s="29"/>
+      <c r="N47" s="27"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B48" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C48" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D48" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E48" s="25" t="s">
+      <c r="B48" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F48" s="15" t="s">
@@ -3482,10 +3523,10 @@
       <c r="I48" s="16">
         <v>2531135082</v>
       </c>
-      <c r="J48" s="17">
+      <c r="J48" s="34">
         <v>20.09</v>
       </c>
-      <c r="K48" s="26" t="s">
+      <c r="K48" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3493,16 +3534,16 @@
       <c r="A49" s="13">
         <v>24</v>
       </c>
-      <c r="B49" s="27" t="s">
+      <c r="B49" s="25" t="s">
         <v>96</v>
       </c>
       <c r="C49" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D49" s="25">
+      <c r="D49" s="23">
         <v>46080</v>
       </c>
-      <c r="E49" s="25">
+      <c r="E49" s="23">
         <v>46090</v>
       </c>
       <c r="F49" s="15" t="s">
@@ -3511,33 +3552,33 @@
       <c r="G49" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="H49" s="25" t="s">
+      <c r="H49" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I49" s="16">
         <v>22374000</v>
       </c>
-      <c r="J49" s="17">
+      <c r="J49" s="34">
         <v>11</v>
       </c>
-      <c r="K49" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L49" s="28"/>
+      <c r="K49" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L49" s="26"/>
       <c r="M49"/>
-      <c r="N49" s="29"/>
+      <c r="N49" s="27"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B50" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D50" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E50" s="25" t="s">
+      <c r="B50" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F50" s="15" t="s">
@@ -3552,10 +3593,10 @@
       <c r="I50" s="16">
         <v>201322000</v>
       </c>
-      <c r="J50" s="17">
+      <c r="J50" s="34">
         <v>11</v>
       </c>
-      <c r="K50" s="26" t="s">
+      <c r="K50" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3563,16 +3604,16 @@
       <c r="A51" s="13">
         <v>25</v>
       </c>
-      <c r="B51" s="27" t="s">
+      <c r="B51" s="25" t="s">
         <v>100</v>
       </c>
       <c r="C51" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="D51" s="25">
+      <c r="D51" s="23">
         <v>46080</v>
       </c>
-      <c r="E51" s="25">
+      <c r="E51" s="23">
         <v>46090</v>
       </c>
       <c r="F51" s="15" t="s">
@@ -3581,33 +3622,33 @@
       <c r="G51" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H51" s="25" t="s">
+      <c r="H51" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I51" s="16">
         <v>148654080</v>
       </c>
-      <c r="J51" s="17">
+      <c r="J51" s="34">
         <v>15.36</v>
       </c>
-      <c r="K51" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L51" s="28"/>
+      <c r="K51" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L51" s="26"/>
       <c r="M51"/>
-      <c r="N51" s="29"/>
+      <c r="N51" s="27"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B52" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C52" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D52" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E52" s="25" t="s">
+      <c r="B52" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F52" s="15" t="s">
@@ -3622,10 +3663,10 @@
       <c r="I52" s="16">
         <v>1337886720</v>
       </c>
-      <c r="J52" s="17">
+      <c r="J52" s="34">
         <v>15.33</v>
       </c>
-      <c r="K52" s="26" t="s">
+      <c r="K52" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3633,16 +3674,16 @@
       <c r="A53" s="13">
         <v>26</v>
       </c>
-      <c r="B53" s="27" t="s">
+      <c r="B53" s="25" t="s">
         <v>103</v>
       </c>
       <c r="C53" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D53" s="25">
+      <c r="D53" s="23">
         <v>46080</v>
       </c>
-      <c r="E53" s="25">
+      <c r="E53" s="23">
         <v>46090</v>
       </c>
       <c r="F53" s="15" t="s">
@@ -3651,33 +3692,33 @@
       <c r="G53" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="H53" s="25" t="s">
+      <c r="H53" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I53" s="16">
         <v>190666872</v>
       </c>
-      <c r="J53" s="17">
+      <c r="J53" s="34">
         <v>71.28</v>
       </c>
-      <c r="K53" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L53" s="28"/>
+      <c r="K53" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L53" s="26"/>
       <c r="M53"/>
-      <c r="N53" s="29"/>
+      <c r="N53" s="27"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B54" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C54" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D54" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E54" s="25" t="s">
+      <c r="B54" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F54" s="15" t="s">
@@ -3692,10 +3733,10 @@
       <c r="I54" s="16">
         <v>1715951952</v>
       </c>
-      <c r="J54" s="17">
+      <c r="J54" s="34">
         <v>71.28</v>
       </c>
-      <c r="K54" s="26" t="s">
+      <c r="K54" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3703,51 +3744,51 @@
       <c r="A55" s="13">
         <v>27</v>
       </c>
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="25" t="s">
         <v>106</v>
       </c>
       <c r="C55" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="D55" s="25">
+      <c r="D55" s="23">
         <v>46080</v>
       </c>
-      <c r="E55" s="25">
+      <c r="E55" s="23">
         <v>46091</v>
       </c>
-      <c r="F55" s="30" t="s">
+      <c r="F55" s="28" t="s">
         <v>108</v>
       </c>
       <c r="G55" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="H55" s="25" t="s">
+      <c r="H55" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I55" s="16">
         <v>101010000</v>
       </c>
-      <c r="J55" s="17">
+      <c r="J55" s="34">
         <v>28.86</v>
       </c>
-      <c r="K55" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L55" s="28"/>
+      <c r="K55" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L55" s="26"/>
       <c r="M55"/>
-      <c r="N55" s="29"/>
+      <c r="N55" s="27"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B56" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C56" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D56" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E56" s="25" t="s">
+      <c r="B56" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E56" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F56" s="15" t="s">
@@ -3762,10 +3803,10 @@
       <c r="I56" s="16">
         <v>1060605000</v>
       </c>
-      <c r="J56" s="17">
+      <c r="J56" s="34">
         <v>28.86</v>
       </c>
-      <c r="K56" s="26" t="s">
+      <c r="K56" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3773,51 +3814,51 @@
       <c r="A57" s="13">
         <v>28</v>
       </c>
-      <c r="B57" s="27" t="s">
+      <c r="B57" s="25" t="s">
         <v>109</v>
       </c>
       <c r="C57" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="D57" s="25">
+      <c r="D57" s="23">
         <v>46065</v>
       </c>
-      <c r="E57" s="25">
+      <c r="E57" s="23">
         <v>46100</v>
       </c>
-      <c r="F57" s="30" t="s">
+      <c r="F57" s="28" t="s">
         <v>75</v>
       </c>
       <c r="G57" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="H57" s="25" t="s">
+      <c r="H57" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I57" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="J57" s="17" t="s">
+      <c r="J57" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="K57" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L57" s="28"/>
+      <c r="K57" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L57" s="26"/>
       <c r="M57"/>
-      <c r="N57" s="29"/>
+      <c r="N57" s="27"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B58" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C58" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D58" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E58" s="25" t="s">
+      <c r="B58" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C58" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E58" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F58" s="15" t="s">
@@ -3830,8 +3871,8 @@
         <v>15</v>
       </c>
       <c r="I58" s="16"/>
-      <c r="J58" s="17"/>
-      <c r="K58" s="26" t="s">
+      <c r="J58" s="34"/>
+      <c r="K58" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3839,51 +3880,51 @@
       <c r="A59" s="13">
         <v>29</v>
       </c>
-      <c r="B59" s="27" t="s">
+      <c r="B59" s="25" t="s">
         <v>112</v>
       </c>
       <c r="C59" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D59" s="25">
+      <c r="D59" s="23">
         <v>46093</v>
       </c>
-      <c r="E59" s="25">
+      <c r="E59" s="23">
         <v>46101</v>
       </c>
-      <c r="F59" s="30" t="s">
+      <c r="F59" s="28" t="s">
         <v>114</v>
       </c>
       <c r="G59" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="H59" s="25" t="s">
+      <c r="H59" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I59" s="16">
         <v>330648000</v>
       </c>
-      <c r="J59" s="17">
+      <c r="J59" s="34">
         <v>71.88</v>
       </c>
-      <c r="K59" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L59" s="28"/>
+      <c r="K59" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L59" s="26"/>
       <c r="M59"/>
-      <c r="N59" s="29"/>
+      <c r="N59" s="27"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B60" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C60" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D60" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E60" s="25" t="s">
+      <c r="B60" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C60" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E60" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F60" s="15" t="s">
@@ -3898,10 +3939,10 @@
       <c r="I60" s="16">
         <v>2975832000</v>
       </c>
-      <c r="J60" s="17">
+      <c r="J60" s="34">
         <v>71.88</v>
       </c>
-      <c r="K60" s="26" t="s">
+      <c r="K60" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3909,51 +3950,51 @@
       <c r="A61" s="13">
         <v>30</v>
       </c>
-      <c r="B61" s="27" t="s">
+      <c r="B61" s="25" t="s">
         <v>115</v>
       </c>
       <c r="C61" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D61" s="25">
+      <c r="D61" s="23">
         <v>46094</v>
       </c>
-      <c r="E61" s="25">
+      <c r="E61" s="23">
         <v>46104</v>
       </c>
-      <c r="F61" s="30" t="s">
+      <c r="F61" s="28" t="s">
         <v>117</v>
       </c>
       <c r="G61" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="H61" s="25" t="s">
+      <c r="H61" s="23" t="s">
         <v>72</v>
       </c>
       <c r="I61" s="16">
         <v>102600000</v>
       </c>
-      <c r="J61" s="17">
+      <c r="J61" s="34">
         <v>10.8</v>
       </c>
-      <c r="K61" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L61" s="28"/>
+      <c r="K61" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L61" s="26"/>
       <c r="M61"/>
-      <c r="N61" s="29"/>
+      <c r="N61" s="27"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B62" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C62" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D62" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E62" s="25" t="s">
+      <c r="B62" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C62" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E62" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F62" s="15" t="s">
@@ -3968,10 +4009,10 @@
       <c r="I62" s="16">
         <v>923400000</v>
       </c>
-      <c r="J62" s="17">
+      <c r="J62" s="34">
         <v>10.8</v>
       </c>
-      <c r="K62" s="26" t="s">
+      <c r="K62" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3979,51 +4020,51 @@
       <c r="A63" s="13">
         <v>31</v>
       </c>
-      <c r="B63" s="27" t="s">
+      <c r="B63" s="25" t="s">
         <v>118</v>
       </c>
       <c r="C63" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="D63" s="25">
+      <c r="D63" s="23">
         <v>46094</v>
       </c>
-      <c r="E63" s="25">
+      <c r="E63" s="23">
         <v>46104</v>
       </c>
-      <c r="F63" s="30" t="s">
+      <c r="F63" s="28" t="s">
         <v>120</v>
       </c>
       <c r="G63" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="H63" s="25" t="s">
+      <c r="H63" s="23" t="s">
         <v>72</v>
       </c>
       <c r="I63" s="16">
         <v>166400000</v>
       </c>
-      <c r="J63" s="17">
+      <c r="J63" s="34">
         <v>41.6</v>
       </c>
-      <c r="K63" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L63" s="28"/>
+      <c r="K63" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L63" s="26"/>
       <c r="M63"/>
-      <c r="N63" s="29"/>
+      <c r="N63" s="27"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B64" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C64" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D64" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E64" s="25" t="s">
+      <c r="B64" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C64" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E64" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F64" s="15" t="s">
@@ -4038,10 +4079,10 @@
       <c r="I64" s="16">
         <v>1733709120</v>
       </c>
-      <c r="J64" s="17">
+      <c r="J64" s="34">
         <v>41.6</v>
       </c>
-      <c r="K64" s="26" t="s">
+      <c r="K64" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4049,51 +4090,51 @@
       <c r="A65" s="13">
         <v>32</v>
       </c>
-      <c r="B65" s="27" t="s">
+      <c r="B65" s="25" t="s">
         <v>121</v>
       </c>
       <c r="C65" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D65" s="25">
+      <c r="D65" s="23">
         <v>46097</v>
       </c>
-      <c r="E65" s="25">
+      <c r="E65" s="23">
         <v>46105</v>
       </c>
-      <c r="F65" s="30" t="s">
+      <c r="F65" s="28" t="s">
         <v>123</v>
       </c>
       <c r="G65" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H65" s="25" t="s">
+      <c r="H65" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I65" s="16">
         <v>71721130</v>
       </c>
-      <c r="J65" s="17">
+      <c r="J65" s="34">
         <v>44.2</v>
       </c>
-      <c r="K65" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L65" s="28"/>
+      <c r="K65" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L65" s="26"/>
       <c r="M65"/>
-      <c r="N65" s="29"/>
+      <c r="N65" s="27"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B66" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C66" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D66" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E66" s="25" t="s">
+      <c r="B66" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F66" s="15" t="s">
@@ -4108,10 +4149,10 @@
       <c r="I66" s="16">
         <v>645490170</v>
       </c>
-      <c r="J66" s="17">
+      <c r="J66" s="34">
         <v>44.2</v>
       </c>
-      <c r="K66" s="26" t="s">
+      <c r="K66" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4119,51 +4160,51 @@
       <c r="A67" s="13">
         <v>33</v>
       </c>
-      <c r="B67" s="27" t="s">
+      <c r="B67" s="25" t="s">
         <v>124</v>
       </c>
       <c r="C67" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="D67" s="25">
+      <c r="D67" s="23">
         <v>46097</v>
       </c>
-      <c r="E67" s="25">
+      <c r="E67" s="23">
         <v>46105</v>
       </c>
-      <c r="F67" s="30" t="s">
+      <c r="F67" s="28" t="s">
         <v>126</v>
       </c>
       <c r="G67" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H67" s="25" t="s">
+      <c r="H67" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I67" s="16">
         <v>61305468</v>
       </c>
-      <c r="J67" s="17">
+      <c r="J67" s="34">
         <v>16.66</v>
       </c>
-      <c r="K67" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L67" s="28"/>
+      <c r="K67" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L67" s="26"/>
       <c r="M67"/>
-      <c r="N67" s="29"/>
+      <c r="N67" s="27"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B68" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C68" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D68" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E68" s="25" t="s">
+      <c r="B68" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C68" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E68" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F68" s="15" t="s">
@@ -4178,10 +4219,10 @@
       <c r="I68" s="16">
         <v>551749212</v>
       </c>
-      <c r="J68" s="17">
+      <c r="J68" s="34">
         <v>16.66</v>
       </c>
-      <c r="K68" s="26" t="s">
+      <c r="K68" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4189,51 +4230,51 @@
       <c r="A69" s="13">
         <v>34</v>
       </c>
-      <c r="B69" s="27" t="s">
+      <c r="B69" s="25" t="s">
         <v>127</v>
       </c>
       <c r="C69" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="D69" s="25">
+      <c r="D69" s="23">
         <v>46101</v>
       </c>
-      <c r="E69" s="25">
+      <c r="E69" s="23">
         <v>46111</v>
       </c>
-      <c r="F69" s="30" t="s">
+      <c r="F69" s="28" t="s">
         <v>129</v>
       </c>
       <c r="G69" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H69" s="25" t="s">
+      <c r="H69" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I69" s="16">
         <v>274669000</v>
       </c>
-      <c r="J69" s="17">
+      <c r="J69" s="34">
         <v>17</v>
       </c>
-      <c r="K69" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L69" s="28"/>
+      <c r="K69" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L69" s="26"/>
       <c r="M69"/>
-      <c r="N69" s="29"/>
+      <c r="N69" s="27"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B70" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C70" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D70" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E70" s="25" t="s">
+      <c r="B70" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E70" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F70" s="15" t="s">
@@ -4248,10 +4289,10 @@
       <c r="I70" s="16">
         <v>1533648200</v>
       </c>
-      <c r="J70" s="17">
+      <c r="J70" s="34">
         <v>17</v>
       </c>
-      <c r="K70" s="26" t="s">
+      <c r="K70" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4259,51 +4300,51 @@
       <c r="A71" s="13">
         <v>35</v>
       </c>
-      <c r="B71" s="27" t="s">
+      <c r="B71" s="25" t="s">
         <v>130</v>
       </c>
       <c r="C71" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="D71" s="25">
+      <c r="D71" s="23">
         <v>46101</v>
       </c>
-      <c r="E71" s="25">
+      <c r="E71" s="23">
         <v>46111</v>
       </c>
-      <c r="F71" s="30" t="s">
+      <c r="F71" s="28" t="s">
         <v>102</v>
       </c>
       <c r="G71" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H71" s="25" t="s">
+      <c r="H71" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I71" s="16">
         <v>79195050</v>
       </c>
-      <c r="J71" s="17">
+      <c r="J71" s="34">
         <v>99</v>
       </c>
-      <c r="K71" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L71" s="28"/>
+      <c r="K71" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L71" s="26"/>
       <c r="M71"/>
-      <c r="N71" s="29"/>
+      <c r="N71" s="27"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B72" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C72" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D72" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E72" s="25" t="s">
+      <c r="B72" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D72" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E72" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F72" s="15" t="s">
@@ -4318,10 +4359,10 @@
       <c r="I72" s="16">
         <v>712725750</v>
       </c>
-      <c r="J72" s="17">
+      <c r="J72" s="34">
         <v>99</v>
       </c>
-      <c r="K72" s="26" t="s">
+      <c r="K72" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4329,51 +4370,51 @@
       <c r="A73" s="13">
         <v>36</v>
       </c>
-      <c r="B73" s="27" t="s">
+      <c r="B73" s="25" t="s">
         <v>132</v>
       </c>
       <c r="C73" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="D73" s="25">
+      <c r="D73" s="23">
         <v>46101</v>
       </c>
-      <c r="E73" s="25">
+      <c r="E73" s="23">
         <v>46111</v>
       </c>
-      <c r="F73" s="30" t="s">
+      <c r="F73" s="28" t="s">
         <v>75</v>
       </c>
       <c r="G73" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="H73" s="25" t="s">
+      <c r="H73" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I73" s="16">
         <v>163901805</v>
       </c>
-      <c r="J73" s="17">
+      <c r="J73" s="34">
         <v>76.260000000000005</v>
       </c>
-      <c r="K73" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L73" s="28"/>
+      <c r="K73" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L73" s="26"/>
       <c r="M73"/>
-      <c r="N73" s="29"/>
+      <c r="N73" s="27"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B74" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C74" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D74" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E74" s="25" t="s">
+      <c r="B74" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C74" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E74" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F74" s="15" t="s">
@@ -4388,10 +4429,10 @@
       <c r="I74" s="16">
         <v>1475081928</v>
       </c>
-      <c r="J74" s="17">
+      <c r="J74" s="34">
         <v>76.260000000000005</v>
       </c>
-      <c r="K74" s="26" t="s">
+      <c r="K74" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4399,51 +4440,51 @@
       <c r="A75" s="13">
         <v>37</v>
       </c>
-      <c r="B75" s="27" t="s">
+      <c r="B75" s="25" t="s">
         <v>134</v>
       </c>
       <c r="C75" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="D75" s="25">
+      <c r="D75" s="23">
         <v>46101</v>
       </c>
-      <c r="E75" s="25">
+      <c r="E75" s="23">
         <v>46111</v>
       </c>
-      <c r="F75" s="30" t="s">
+      <c r="F75" s="28" t="s">
         <v>117</v>
       </c>
       <c r="G75" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H75" s="25" t="s">
+      <c r="H75" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I75" s="16">
         <v>99840000</v>
       </c>
-      <c r="J75" s="17">
+      <c r="J75" s="34">
         <v>40</v>
       </c>
-      <c r="K75" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L75" s="28"/>
+      <c r="K75" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L75" s="26"/>
       <c r="M75"/>
-      <c r="N75" s="29"/>
+      <c r="N75" s="27"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B76" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C76" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D76" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E76" s="25" t="s">
+      <c r="B76" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C76" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E76" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F76" s="15" t="s">
@@ -4458,10 +4499,10 @@
       <c r="I76" s="16">
         <v>399360000</v>
       </c>
-      <c r="J76" s="17">
+      <c r="J76" s="34">
         <v>40</v>
       </c>
-      <c r="K76" s="26" t="s">
+      <c r="K76" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4469,51 +4510,51 @@
       <c r="A77" s="13">
         <v>38</v>
       </c>
-      <c r="B77" s="27" t="s">
+      <c r="B77" s="25" t="s">
         <v>136</v>
       </c>
       <c r="C77" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="D77" s="25">
+      <c r="D77" s="23">
         <v>46104</v>
       </c>
-      <c r="E77" s="25">
+      <c r="E77" s="23">
         <v>46112</v>
       </c>
-      <c r="F77" s="30" t="s">
+      <c r="F77" s="28" t="s">
         <v>138</v>
       </c>
       <c r="G77" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="H77" s="25" t="s">
+      <c r="H77" s="23" t="s">
         <v>139</v>
       </c>
       <c r="I77" s="16">
         <v>66660000</v>
       </c>
-      <c r="J77" s="17">
+      <c r="J77" s="34">
         <v>60</v>
       </c>
-      <c r="K77" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L77" s="28"/>
+      <c r="K77" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L77" s="26"/>
       <c r="M77"/>
-      <c r="N77" s="29"/>
+      <c r="N77" s="27"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B78" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C78" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D78" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E78" s="25" t="s">
+      <c r="B78" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E78" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F78" s="15" t="s">
@@ -4528,10 +4569,10 @@
       <c r="I78" s="16">
         <v>377748000</v>
       </c>
-      <c r="J78" s="17">
+      <c r="J78" s="34">
         <v>60</v>
       </c>
-      <c r="K78" s="26" t="s">
+      <c r="K78" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4539,51 +4580,51 @@
       <c r="A79" s="13">
         <v>39</v>
       </c>
-      <c r="B79" s="27" t="s">
+      <c r="B79" s="25" t="s">
         <v>140</v>
       </c>
       <c r="C79" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="D79" s="25">
+      <c r="D79" s="23">
         <v>46104</v>
       </c>
-      <c r="E79" s="25">
+      <c r="E79" s="23">
         <v>46112</v>
       </c>
-      <c r="F79" s="30" t="s">
+      <c r="F79" s="28" t="s">
         <v>142</v>
       </c>
       <c r="G79" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H79" s="25" t="s">
+      <c r="H79" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I79" s="16">
         <v>96000000</v>
       </c>
-      <c r="J79" s="17">
+      <c r="J79" s="34">
         <v>40</v>
       </c>
-      <c r="K79" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L79" s="28"/>
+      <c r="K79" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L79" s="26"/>
       <c r="M79"/>
-      <c r="N79" s="29"/>
+      <c r="N79" s="27"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B80" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C80" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D80" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E80" s="25" t="s">
+      <c r="B80" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C80" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E80" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F80" s="15" t="s">
@@ -4598,10 +4639,10 @@
       <c r="I80" s="16">
         <v>384000000</v>
       </c>
-      <c r="J80" s="17">
+      <c r="J80" s="34">
         <v>40</v>
       </c>
-      <c r="K80" s="26" t="s">
+      <c r="K80" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4609,51 +4650,51 @@
       <c r="A81" s="13">
         <v>40</v>
       </c>
-      <c r="B81" s="27" t="s">
+      <c r="B81" s="25" t="s">
         <v>143</v>
       </c>
       <c r="C81" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="D81" s="25">
+      <c r="D81" s="23">
         <v>46120</v>
       </c>
-      <c r="E81" s="25">
+      <c r="E81" s="23">
         <v>46128</v>
       </c>
-      <c r="F81" s="30" t="s">
+      <c r="F81" s="28" t="s">
         <v>145</v>
       </c>
       <c r="G81" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H81" s="25" t="s">
+      <c r="H81" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I81" s="16">
         <v>440069080</v>
       </c>
-      <c r="J81" s="17">
+      <c r="J81" s="34">
         <v>324.2</v>
       </c>
-      <c r="K81" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="L81" s="28"/>
+      <c r="K81" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="L81" s="26"/>
       <c r="M81"/>
-      <c r="N81" s="29"/>
+      <c r="N81" s="27"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B82" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C82" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D82" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E82" s="25" t="s">
+      <c r="B82" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E82" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F82" s="15" t="s">
@@ -4668,10 +4709,10 @@
       <c r="I82" s="16">
         <v>4620660500</v>
       </c>
-      <c r="J82" s="17">
+      <c r="J82" s="34">
         <v>324.2</v>
       </c>
-      <c r="K82" s="26" t="s">
+      <c r="K82" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4679,48 +4720,48 @@
       <c r="A83" s="13">
         <v>41</v>
       </c>
-      <c r="B83" s="27" t="s">
+      <c r="B83" s="25" t="s">
         <v>146</v>
       </c>
       <c r="C83" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="D83" s="25">
+      <c r="D83" s="23">
         <v>46121</v>
       </c>
-      <c r="E83" s="25">
+      <c r="E83" s="23">
         <v>46129</v>
       </c>
-      <c r="F83" s="30" t="s">
+      <c r="F83" s="28" t="s">
         <v>148</v>
       </c>
       <c r="G83" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H83" s="25" t="s">
+      <c r="H83" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I83" s="16">
         <v>260396460.00000003</v>
       </c>
-      <c r="J83" s="17">
+      <c r="J83" s="34">
         <v>39.880000000000003</v>
       </c>
-      <c r="K83" s="26" t="s">
+      <c r="K83" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B84" s="27" t="s">
+      <c r="B84" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C84" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D84" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E84" s="25" t="s">
+      <c r="D84" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E84" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F84" s="15" t="s">
@@ -4735,10 +4776,10 @@
       <c r="I84" s="16">
         <v>2734124944</v>
       </c>
-      <c r="J84" s="17">
+      <c r="J84" s="34">
         <v>39.880000000000003</v>
       </c>
-      <c r="K84" s="26" t="s">
+      <c r="K84" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4746,51 +4787,51 @@
       <c r="A85" s="13">
         <v>42</v>
       </c>
-      <c r="B85" s="27" t="s">
+      <c r="B85" s="25" t="s">
         <v>149</v>
       </c>
       <c r="C85" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="D85" s="25">
+      <c r="D85" s="23">
         <v>46121</v>
       </c>
-      <c r="E85" s="25">
+      <c r="E85" s="23">
         <v>46129</v>
       </c>
-      <c r="F85" s="30" t="s">
+      <c r="F85" s="28" t="s">
         <v>151</v>
       </c>
       <c r="G85" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H85" s="25" t="s">
+      <c r="H85" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I85" s="16">
         <v>122392440</v>
       </c>
-      <c r="J85" s="17">
+      <c r="J85" s="34">
         <v>7.62</v>
       </c>
-      <c r="K85" s="26" t="s">
+      <c r="K85" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B86" s="27" t="s">
+      <c r="B86" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C86" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D86" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E86" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="F86" s="30" t="s">
+      <c r="D86" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E86" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F86" s="28" t="s">
         <v>15</v>
       </c>
       <c r="G86" s="15" t="s">
@@ -4802,10 +4843,10 @@
       <c r="I86" s="16">
         <v>1285109190</v>
       </c>
-      <c r="J86" s="17">
+      <c r="J86" s="34">
         <v>7.62</v>
       </c>
-      <c r="K86" s="26" t="s">
+      <c r="K86" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4813,48 +4854,48 @@
       <c r="A87" s="13">
         <v>43</v>
       </c>
-      <c r="B87" s="27" t="s">
+      <c r="B87" s="25" t="s">
         <v>152</v>
       </c>
       <c r="C87" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="D87" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="E87" s="25">
+      <c r="D87" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E87" s="23">
         <v>46129</v>
       </c>
-      <c r="F87" s="30" t="s">
+      <c r="F87" s="28" t="s">
         <v>21</v>
       </c>
       <c r="G87" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H87" s="25" t="s">
+      <c r="H87" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I87" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="J87" s="16" t="s">
+      <c r="J87" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="K87" s="26" t="s">
+      <c r="K87" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B88" s="27" t="s">
+      <c r="B88" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C88" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D88" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E88" s="25" t="s">
+      <c r="D88" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E88" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F88" s="15" t="s">
@@ -4869,10 +4910,10 @@
       <c r="I88" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="J88" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K88" s="26" t="s">
+      <c r="J88" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="K88" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4880,48 +4921,48 @@
       <c r="A89" s="13">
         <v>44</v>
       </c>
-      <c r="B89" s="27" t="s">
+      <c r="B89" s="25" t="s">
         <v>155</v>
       </c>
       <c r="C89" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="D89" s="25">
+      <c r="D89" s="23">
         <v>46125</v>
       </c>
-      <c r="E89" s="25">
+      <c r="E89" s="23">
         <v>46133</v>
       </c>
-      <c r="F89" s="30" t="s">
+      <c r="F89" s="28" t="s">
         <v>157</v>
       </c>
       <c r="G89" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="H89" s="25" t="s">
+      <c r="H89" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I89" s="16">
         <v>1749307824</v>
       </c>
-      <c r="J89" s="17">
+      <c r="J89" s="34">
         <v>209.88</v>
       </c>
-      <c r="K89" s="26" t="s">
+      <c r="K89" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B90" s="27" t="s">
+      <c r="B90" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C90" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D90" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E90" s="25" t="s">
+      <c r="D90" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E90" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F90" s="15" t="s">
@@ -4936,10 +4977,10 @@
       <c r="I90" s="16">
         <v>21385239876</v>
       </c>
-      <c r="J90" s="17">
+      <c r="J90" s="34">
         <v>209.88</v>
       </c>
-      <c r="K90" s="26" t="s">
+      <c r="K90" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -4947,48 +4988,48 @@
       <c r="A91" s="13">
         <v>45</v>
       </c>
-      <c r="B91" s="27" t="s">
+      <c r="B91" s="25" t="s">
         <v>158</v>
       </c>
       <c r="C91" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="D91" s="25">
+      <c r="D91" s="23">
         <v>46127</v>
       </c>
-      <c r="E91" s="25">
+      <c r="E91" s="23">
         <v>46135</v>
       </c>
-      <c r="F91" s="30" t="s">
+      <c r="F91" s="28" t="s">
         <v>160</v>
       </c>
       <c r="G91" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="H91" s="25" t="s">
+      <c r="H91" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I91" s="16">
         <v>454925730</v>
       </c>
-      <c r="J91" s="17">
+      <c r="J91" s="34">
         <v>77.7</v>
       </c>
-      <c r="K91" s="26" t="s">
+      <c r="K91" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B92" s="27" t="s">
+      <c r="B92" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C92" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D92" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E92" s="25" t="s">
+      <c r="D92" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E92" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F92" s="15" t="s">
@@ -5003,10 +5044,10 @@
       <c r="I92" s="16">
         <v>4776646350</v>
       </c>
-      <c r="J92" s="17">
+      <c r="J92" s="34">
         <v>77.7</v>
       </c>
-      <c r="K92" s="26" t="s">
+      <c r="K92" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5014,48 +5055,48 @@
       <c r="A93" s="13">
         <v>46</v>
       </c>
-      <c r="B93" s="27" t="s">
+      <c r="B93" s="25" t="s">
         <v>161</v>
       </c>
       <c r="C93" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="D93" s="25">
+      <c r="D93" s="23">
         <v>46132</v>
       </c>
-      <c r="E93" s="25">
+      <c r="E93" s="23">
         <v>46140</v>
       </c>
-      <c r="F93" s="30" t="s">
+      <c r="F93" s="28" t="s">
         <v>163</v>
       </c>
       <c r="G93" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="H93" s="25" t="s">
+      <c r="H93" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I93" s="16">
         <v>505458876</v>
       </c>
-      <c r="J93" s="17">
+      <c r="J93" s="34">
         <v>183.2</v>
       </c>
-      <c r="K93" s="26" t="s">
+      <c r="K93" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B94" s="27" t="s">
+      <c r="B94" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C94" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D94" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E94" s="25" t="s">
+      <c r="D94" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E94" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F94" s="15" t="s">
@@ -5070,10 +5111,10 @@
       <c r="I94" s="16">
         <v>2400916608</v>
       </c>
-      <c r="J94" s="17">
+      <c r="J94" s="34">
         <v>183.2</v>
       </c>
-      <c r="K94" s="26" t="s">
+      <c r="K94" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5081,48 +5122,48 @@
       <c r="A95" s="13">
         <v>47</v>
       </c>
-      <c r="B95" s="27" t="s">
+      <c r="B95" s="25" t="s">
         <v>164</v>
       </c>
       <c r="C95" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="D95" s="25">
+      <c r="D95" s="23">
         <v>46132</v>
       </c>
-      <c r="E95" s="25">
+      <c r="E95" s="23">
         <v>46140</v>
       </c>
-      <c r="F95" s="30" t="s">
+      <c r="F95" s="28" t="s">
         <v>166</v>
       </c>
       <c r="G95" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H95" s="25" t="s">
+      <c r="H95" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I95" s="16">
         <v>130272848</v>
       </c>
-      <c r="J95" s="17">
+      <c r="J95" s="34">
         <v>27.64</v>
       </c>
-      <c r="K95" s="26" t="s">
+      <c r="K95" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B96" s="27" t="s">
+      <c r="B96" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C96" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D96" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E96" s="25" t="s">
+      <c r="D96" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E96" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F96" s="15" t="s">
@@ -5137,10 +5178,10 @@
       <c r="I96" s="16">
         <v>1172405880</v>
       </c>
-      <c r="J96" s="17">
+      <c r="J96" s="34">
         <v>27.64</v>
       </c>
-      <c r="K96" s="26" t="s">
+      <c r="K96" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5148,48 +5189,48 @@
       <c r="A97" s="13">
         <v>48</v>
       </c>
-      <c r="B97" s="27" t="s">
+      <c r="B97" s="25" t="s">
         <v>167</v>
       </c>
       <c r="C97" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="D97" s="25">
+      <c r="D97" s="23">
         <v>46133</v>
       </c>
-      <c r="E97" s="25">
+      <c r="E97" s="23">
         <v>46141</v>
       </c>
-      <c r="F97" s="30" t="s">
+      <c r="F97" s="28" t="s">
         <v>169</v>
       </c>
       <c r="G97" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="H97" s="25" t="s">
+      <c r="H97" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I97" s="16">
         <v>105970722</v>
       </c>
-      <c r="J97" s="17">
+      <c r="J97" s="34">
         <v>24.86</v>
       </c>
-      <c r="K97" s="26" t="s">
+      <c r="K97" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B98" s="27" t="s">
+      <c r="B98" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C98" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D98" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E98" s="25" t="s">
+      <c r="D98" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E98" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F98" s="15" t="s">
@@ -5204,10 +5245,10 @@
       <c r="I98" s="16">
         <v>953731526</v>
       </c>
-      <c r="J98" s="17">
+      <c r="J98" s="34">
         <v>24.86</v>
       </c>
-      <c r="K98" s="26" t="s">
+      <c r="K98" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5215,48 +5256,48 @@
       <c r="A99" s="13">
         <v>49</v>
       </c>
-      <c r="B99" s="27" t="s">
+      <c r="B99" s="25" t="s">
         <v>170</v>
       </c>
       <c r="C99" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="D99" s="25">
+      <c r="D99" s="23">
         <v>46136</v>
       </c>
-      <c r="E99" s="25">
+      <c r="E99" s="23">
         <v>46147</v>
       </c>
-      <c r="F99" s="30" t="s">
+      <c r="F99" s="28" t="s">
         <v>172</v>
       </c>
       <c r="G99" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H99" s="25" t="s">
+      <c r="H99" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I99" s="16">
         <v>82956700</v>
       </c>
-      <c r="J99" s="17">
+      <c r="J99" s="34">
         <v>98.5</v>
       </c>
-      <c r="K99" s="26" t="s">
+      <c r="K99" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B100" s="27" t="s">
+      <c r="B100" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C100" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D100" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E100" s="25" t="s">
+      <c r="D100" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E100" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F100" s="15" t="s">
@@ -5271,10 +5312,10 @@
       <c r="I100" s="16">
         <v>746595525</v>
       </c>
-      <c r="J100" s="17">
+      <c r="J100" s="34">
         <v>98.5</v>
       </c>
-      <c r="K100" s="26" t="s">
+      <c r="K100" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5282,48 +5323,48 @@
       <c r="A101" s="13">
         <v>50</v>
       </c>
-      <c r="B101" s="27" t="s">
+      <c r="B101" s="25" t="s">
         <v>173</v>
       </c>
       <c r="C101" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="D101" s="25">
+      <c r="D101" s="23">
         <v>46139</v>
       </c>
-      <c r="E101" s="25">
+      <c r="E101" s="23">
         <v>46148</v>
       </c>
-      <c r="F101" s="30" t="s">
+      <c r="F101" s="28" t="s">
         <v>175</v>
       </c>
       <c r="G101" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H101" s="25" t="s">
+      <c r="H101" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I101" s="16">
         <v>106191000</v>
       </c>
-      <c r="J101" s="17">
+      <c r="J101" s="34">
         <v>39.33</v>
       </c>
-      <c r="K101" s="26" t="s">
+      <c r="K101" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B102" s="27" t="s">
+      <c r="B102" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C102" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D102" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E102" s="25" t="s">
+      <c r="D102" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E102" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F102" s="15" t="s">
@@ -5338,10 +5379,10 @@
       <c r="I102" s="16">
         <v>955719000</v>
       </c>
-      <c r="J102" s="17">
+      <c r="J102" s="34">
         <v>39.33</v>
       </c>
-      <c r="K102" s="26" t="s">
+      <c r="K102" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5349,48 +5390,48 @@
       <c r="A103" s="13">
         <v>51</v>
       </c>
-      <c r="B103" s="27" t="s">
+      <c r="B103" s="25" t="s">
         <v>176</v>
       </c>
       <c r="C103" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="D103" s="25">
+      <c r="D103" s="23">
         <v>46142</v>
       </c>
-      <c r="E103" s="25">
+      <c r="E103" s="23">
         <v>46153</v>
       </c>
-      <c r="F103" s="30" t="s">
+      <c r="F103" s="28" t="s">
         <v>178</v>
       </c>
       <c r="G103" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H103" s="25" t="s">
+      <c r="H103" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I103" s="16">
         <v>87868424</v>
       </c>
-      <c r="J103" s="17">
+      <c r="J103" s="34">
         <v>26.36</v>
       </c>
-      <c r="K103" s="26" t="s">
+      <c r="K103" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B104" s="27" t="s">
+      <c r="B104" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C104" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D104" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E104" s="25" t="s">
+      <c r="D104" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E104" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F104" s="15" t="s">
@@ -5405,10 +5446,10 @@
       <c r="I104" s="16">
         <v>790800000</v>
       </c>
-      <c r="J104" s="17">
+      <c r="J104" s="34">
         <v>26.36</v>
       </c>
-      <c r="K104" s="26" t="s">
+      <c r="K104" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5416,48 +5457,48 @@
       <c r="A105" s="13">
         <v>52</v>
       </c>
-      <c r="B105" s="27" t="s">
+      <c r="B105" s="25" t="s">
         <v>179</v>
       </c>
       <c r="C105" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="D105" s="25">
+      <c r="D105" s="23">
         <v>46147</v>
       </c>
-      <c r="E105" s="25">
+      <c r="E105" s="23">
         <v>46155</v>
       </c>
-      <c r="F105" s="30" t="s">
+      <c r="F105" s="28" t="s">
         <v>181</v>
       </c>
       <c r="G105" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H105" s="25" t="s">
+      <c r="H105" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I105" s="16">
         <v>84375780</v>
       </c>
-      <c r="J105" s="17">
+      <c r="J105" s="34">
         <v>20.100000000000001</v>
       </c>
-      <c r="K105" s="26" t="s">
+      <c r="K105" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B106" s="27" t="s">
+      <c r="B106" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C106" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D106" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E106" s="25" t="s">
+      <c r="D106" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E106" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F106" s="15" t="s">
@@ -5472,10 +5513,10 @@
       <c r="I106" s="16">
         <v>885919560</v>
       </c>
-      <c r="J106" s="17">
+      <c r="J106" s="34">
         <v>20.100000000000001</v>
       </c>
-      <c r="K106" s="26" t="s">
+      <c r="K106" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5483,48 +5524,48 @@
       <c r="A107" s="13">
         <v>53</v>
       </c>
-      <c r="B107" s="27" t="s">
+      <c r="B107" s="25" t="s">
         <v>182</v>
       </c>
       <c r="C107" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="D107" s="25">
+      <c r="D107" s="23">
         <v>46147</v>
       </c>
-      <c r="E107" s="25">
+      <c r="E107" s="23">
         <v>46155</v>
       </c>
-      <c r="F107" s="30" t="s">
+      <c r="F107" s="28" t="s">
         <v>184</v>
       </c>
       <c r="G107" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="H107" s="25" t="s">
+      <c r="H107" s="23" t="s">
         <v>72</v>
       </c>
       <c r="I107" s="16">
         <v>422583000</v>
       </c>
-      <c r="J107" s="17">
+      <c r="J107" s="34">
         <v>10.5</v>
       </c>
-      <c r="K107" s="26" t="s">
+      <c r="K107" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B108" s="27" t="s">
+      <c r="B108" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C108" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D108" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E108" s="25" t="s">
+      <c r="D108" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E108" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F108" s="15" t="s">
@@ -5539,10 +5580,10 @@
       <c r="I108" s="16">
         <v>2007253500</v>
       </c>
-      <c r="J108" s="17">
+      <c r="J108" s="34">
         <v>10.5</v>
       </c>
-      <c r="K108" s="26" t="s">
+      <c r="K108" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5550,48 +5591,48 @@
       <c r="A109" s="13">
         <v>54</v>
       </c>
-      <c r="B109" s="27" t="s">
+      <c r="B109" s="25" t="s">
         <v>185</v>
       </c>
       <c r="C109" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="D109" s="25">
+      <c r="D109" s="23">
         <v>46150</v>
       </c>
-      <c r="E109" s="25">
+      <c r="E109" s="23">
         <v>46160</v>
       </c>
-      <c r="F109" s="30" t="s">
+      <c r="F109" s="28" t="s">
         <v>187</v>
       </c>
       <c r="G109" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H109" s="25" t="s">
+      <c r="H109" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I109" s="16">
         <v>150060000</v>
       </c>
-      <c r="J109" s="17">
+      <c r="J109" s="34">
         <v>30.5</v>
       </c>
-      <c r="K109" s="26" t="s">
+      <c r="K109" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B110" s="27" t="s">
+      <c r="B110" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C110" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D110" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E110" s="25" t="s">
+      <c r="D110" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E110" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F110" s="15" t="s">
@@ -5606,10 +5647,10 @@
       <c r="I110" s="16">
         <v>600240000</v>
       </c>
-      <c r="J110" s="17">
+      <c r="J110" s="34">
         <v>30.5</v>
       </c>
-      <c r="K110" s="26" t="s">
+      <c r="K110" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5617,48 +5658,48 @@
       <c r="A111" s="13">
         <v>55</v>
       </c>
-      <c r="B111" s="27" t="s">
+      <c r="B111" s="25" t="s">
         <v>188</v>
       </c>
       <c r="C111" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="D111" s="25">
+      <c r="D111" s="23">
         <v>46154</v>
       </c>
-      <c r="E111" s="25">
+      <c r="E111" s="23">
         <v>46162</v>
       </c>
-      <c r="F111" s="30" t="s">
+      <c r="F111" s="28" t="s">
         <v>117</v>
       </c>
       <c r="G111" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H111" s="25" t="s">
+      <c r="H111" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I111" s="16">
         <v>174402675</v>
       </c>
-      <c r="J111" s="17">
+      <c r="J111" s="34">
         <v>60.3</v>
       </c>
-      <c r="K111" s="26" t="s">
+      <c r="K111" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B112" s="27" t="s">
+      <c r="B112" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C112" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D112" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E112" s="25" t="s">
+      <c r="D112" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E112" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F112" s="15" t="s">
@@ -5673,10 +5714,10 @@
       <c r="I112" s="16">
         <v>697607685</v>
       </c>
-      <c r="J112" s="17">
+      <c r="J112" s="34">
         <v>60.3</v>
       </c>
-      <c r="K112" s="26" t="s">
+      <c r="K112" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5684,48 +5725,48 @@
       <c r="A113" s="13">
         <v>56</v>
       </c>
-      <c r="B113" s="27" t="s">
+      <c r="B113" s="25" t="s">
         <v>190</v>
       </c>
       <c r="C113" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="D113" s="25">
+      <c r="D113" s="23">
         <v>46154</v>
       </c>
-      <c r="E113" s="25">
+      <c r="E113" s="23">
         <v>46162</v>
       </c>
-      <c r="F113" s="30" t="s">
+      <c r="F113" s="28" t="s">
         <v>192</v>
       </c>
       <c r="G113" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H113" s="25" t="s">
+      <c r="H113" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I113" s="16">
         <v>172405870</v>
       </c>
-      <c r="J113" s="17">
+      <c r="J113" s="34">
         <v>26.39</v>
       </c>
-      <c r="K113" s="26" t="s">
+      <c r="K113" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B114" s="27" t="s">
+      <c r="B114" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C114" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D114" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E114" s="25" t="s">
+      <c r="D114" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E114" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F114" s="15" t="s">
@@ -5740,10 +5781,10 @@
       <c r="I114" s="16">
         <v>1810261635</v>
       </c>
-      <c r="J114" s="17">
+      <c r="J114" s="34">
         <v>26.39</v>
       </c>
-      <c r="K114" s="26" t="s">
+      <c r="K114" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5751,48 +5792,48 @@
       <c r="A115" s="13">
         <v>57</v>
       </c>
-      <c r="B115" s="27" t="s">
+      <c r="B115" s="25" t="s">
         <v>193</v>
       </c>
       <c r="C115" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="D115" s="25">
+      <c r="D115" s="23">
         <v>46156</v>
       </c>
-      <c r="E115" s="25">
+      <c r="E115" s="23">
         <v>46164</v>
       </c>
-      <c r="F115" s="30" t="s">
+      <c r="F115" s="28" t="s">
         <v>195</v>
       </c>
       <c r="G115" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="H115" s="25" t="s">
+      <c r="H115" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I115" s="16">
         <v>62687170</v>
       </c>
-      <c r="J115" s="17">
+      <c r="J115" s="34">
         <v>75.7</v>
       </c>
-      <c r="K115" s="26" t="s">
+      <c r="K115" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B116" s="27" t="s">
+      <c r="B116" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C116" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D116" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E116" s="25" t="s">
+      <c r="D116" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E116" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F116" s="15" t="s">
@@ -5807,10 +5848,10 @@
       <c r="I116" s="16">
         <v>607712030</v>
       </c>
-      <c r="J116" s="17">
+      <c r="J116" s="34">
         <v>75.7</v>
       </c>
-      <c r="K116" s="26" t="s">
+      <c r="K116" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5818,48 +5859,48 @@
       <c r="A117" s="13">
         <v>58</v>
       </c>
-      <c r="B117" s="27" t="s">
+      <c r="B117" s="25" t="s">
         <v>196</v>
       </c>
       <c r="C117" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="D117" s="25">
+      <c r="D117" s="23">
         <v>46160</v>
       </c>
-      <c r="E117" s="25">
+      <c r="E117" s="23">
         <v>46169</v>
       </c>
-      <c r="F117" s="30" t="s">
+      <c r="F117" s="28" t="s">
         <v>98</v>
       </c>
       <c r="G117" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H117" s="25" t="s">
+      <c r="H117" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I117" s="16">
         <v>63002240</v>
       </c>
-      <c r="J117" s="17">
+      <c r="J117" s="34">
         <v>32.799999999999997</v>
       </c>
-      <c r="K117" s="26" t="s">
+      <c r="K117" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B118" s="27" t="s">
+      <c r="B118" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C118" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D118" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E118" s="25" t="s">
+      <c r="D118" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E118" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F118" s="15" t="s">
@@ -5874,10 +5915,10 @@
       <c r="I118" s="16">
         <v>566997200</v>
       </c>
-      <c r="J118" s="17">
+      <c r="J118" s="34">
         <v>32.799999999999997</v>
       </c>
-      <c r="K118" s="26" t="s">
+      <c r="K118" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5885,48 +5926,48 @@
       <c r="A119" s="13">
         <v>59</v>
       </c>
-      <c r="B119" s="27" t="s">
+      <c r="B119" s="25" t="s">
         <v>198</v>
       </c>
       <c r="C119" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="D119" s="25">
+      <c r="D119" s="23">
         <v>46160</v>
       </c>
-      <c r="E119" s="25">
+      <c r="E119" s="23">
         <v>46169</v>
       </c>
-      <c r="F119" s="30" t="s">
+      <c r="F119" s="28" t="s">
         <v>200</v>
       </c>
       <c r="G119" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H119" s="25" t="s">
+      <c r="H119" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I119" s="16">
         <v>50327400</v>
       </c>
-      <c r="J119" s="17">
+      <c r="J119" s="34">
         <v>55.5</v>
       </c>
-      <c r="K119" s="26" t="s">
+      <c r="K119" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B120" s="27" t="s">
+      <c r="B120" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C120" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D120" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E120" s="25" t="s">
+      <c r="D120" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E120" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F120" s="15" t="s">
@@ -5941,10 +5982,10 @@
       <c r="I120" s="16">
         <v>452946600</v>
       </c>
-      <c r="J120" s="17">
+      <c r="J120" s="34">
         <v>55.5</v>
       </c>
-      <c r="K120" s="26" t="s">
+      <c r="K120" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5952,48 +5993,48 @@
       <c r="A121" s="13">
         <v>60</v>
       </c>
-      <c r="B121" s="27" t="s">
+      <c r="B121" s="25" t="s">
         <v>201</v>
       </c>
       <c r="C121" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="D121" s="25">
+      <c r="D121" s="23">
         <v>46160</v>
       </c>
-      <c r="E121" s="25">
+      <c r="E121" s="23">
         <v>46169</v>
       </c>
-      <c r="F121" s="30" t="s">
+      <c r="F121" s="28" t="s">
         <v>203</v>
       </c>
       <c r="G121" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H121" s="25" t="s">
+      <c r="H121" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I121" s="16">
         <v>110001660</v>
       </c>
-      <c r="J121" s="17">
+      <c r="J121" s="34">
         <v>20.81</v>
       </c>
-      <c r="K121" s="26" t="s">
+      <c r="K121" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B122" s="27" t="s">
+      <c r="B122" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C122" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D122" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E122" s="25" t="s">
+      <c r="D122" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E122" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F122" s="15" t="s">
@@ -6008,10 +6049,10 @@
       <c r="I122" s="16">
         <v>1154996620</v>
       </c>
-      <c r="J122" s="17">
+      <c r="J122" s="34">
         <v>20.81</v>
       </c>
-      <c r="K122" s="26" t="s">
+      <c r="K122" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -6019,48 +6060,48 @@
       <c r="A123" s="13">
         <v>61</v>
       </c>
-      <c r="B123" s="27" t="s">
+      <c r="B123" s="25" t="s">
         <v>204</v>
       </c>
       <c r="C123" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="D123" s="25">
+      <c r="D123" s="23">
         <v>46162</v>
       </c>
-      <c r="E123" s="25">
+      <c r="E123" s="23">
         <v>46171</v>
       </c>
-      <c r="F123" s="30" t="s">
+      <c r="F123" s="28" t="s">
         <v>75</v>
       </c>
       <c r="G123" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="H123" s="25" t="s">
+      <c r="H123" s="23" t="s">
         <v>206</v>
       </c>
       <c r="I123" s="16">
         <v>138044640</v>
       </c>
-      <c r="J123" s="17">
+      <c r="J123" s="34">
         <v>18.8</v>
       </c>
-      <c r="K123" s="26" t="s">
+      <c r="K123" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B124" s="27" t="s">
+      <c r="B124" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C124" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D124" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E124" s="25" t="s">
+      <c r="D124" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E124" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F124" s="15" t="s">
@@ -6075,10 +6116,10 @@
       <c r="I124" s="16">
         <v>1449457440</v>
       </c>
-      <c r="J124" s="17">
+      <c r="J124" s="34">
         <v>18.8</v>
       </c>
-      <c r="K124" s="26" t="s">
+      <c r="K124" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -6086,48 +6127,48 @@
       <c r="A125" s="13">
         <v>62</v>
       </c>
-      <c r="B125" s="27" t="s">
+      <c r="B125" s="25" t="s">
         <v>207</v>
       </c>
       <c r="C125" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="D125" s="25">
+      <c r="D125" s="23">
         <v>46168</v>
       </c>
-      <c r="E125" s="25">
+      <c r="E125" s="23">
         <v>46176</v>
       </c>
-      <c r="F125" s="30" t="s">
+      <c r="F125" s="28" t="s">
         <v>209</v>
       </c>
       <c r="G125" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H125" s="25" t="s">
+      <c r="H125" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I125" s="16">
         <v>87600000</v>
       </c>
-      <c r="J125" s="17">
+      <c r="J125" s="34">
         <v>14.6</v>
       </c>
-      <c r="K125" s="26" t="s">
+      <c r="K125" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B126" s="27" t="s">
+      <c r="B126" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C126" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D126" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E126" s="25" t="s">
+      <c r="D126" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E126" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F126" s="15" t="s">
@@ -6142,10 +6183,10 @@
       <c r="I126" s="16">
         <v>496400000</v>
       </c>
-      <c r="J126" s="17">
+      <c r="J126" s="34">
         <v>14.6</v>
       </c>
-      <c r="K126" s="26" t="s">
+      <c r="K126" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -6153,48 +6194,48 @@
       <c r="A127" s="13">
         <v>63</v>
       </c>
-      <c r="B127" s="27" t="s">
+      <c r="B127" s="25" t="s">
         <v>210</v>
       </c>
       <c r="C127" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="D127" s="25">
+      <c r="D127" s="23">
         <v>46170</v>
       </c>
-      <c r="E127" s="25">
+      <c r="E127" s="23">
         <v>46178</v>
       </c>
-      <c r="F127" s="30" t="s">
+      <c r="F127" s="28" t="s">
         <v>212</v>
       </c>
       <c r="G127" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="H127" s="25" t="s">
+      <c r="H127" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I127" s="16">
         <v>577454240</v>
       </c>
-      <c r="J127" s="17">
+      <c r="J127" s="34">
         <v>66.400000000000006</v>
       </c>
-      <c r="K127" s="26" t="s">
+      <c r="K127" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B128" s="27" t="s">
+      <c r="B128" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C128" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D128" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E128" s="25" t="s">
+      <c r="D128" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E128" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F128" s="15" t="s">
@@ -6209,10 +6250,10 @@
       <c r="I128" s="16">
         <v>6217689360</v>
       </c>
-      <c r="J128" s="17">
+      <c r="J128" s="34">
         <v>66.400000000000006</v>
       </c>
-      <c r="K128" s="26" t="s">
+      <c r="K128" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -6220,48 +6261,48 @@
       <c r="A129" s="13">
         <v>64</v>
       </c>
-      <c r="B129" s="27" t="s">
+      <c r="B129" s="25" t="s">
         <v>213</v>
       </c>
       <c r="C129" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="D129" s="25">
+      <c r="D129" s="23">
         <v>46170</v>
       </c>
-      <c r="E129" s="25">
+      <c r="E129" s="23">
         <v>46178</v>
       </c>
-      <c r="F129" s="30" t="s">
+      <c r="F129" s="28" t="s">
         <v>215</v>
       </c>
       <c r="G129" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H129" s="25" t="s">
+      <c r="H129" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I129" s="16">
         <v>136342761</v>
       </c>
-      <c r="J129" s="17">
+      <c r="J129" s="34">
         <v>96.06</v>
       </c>
-      <c r="K129" s="26" t="s">
+      <c r="K129" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B130" s="27" t="s">
+      <c r="B130" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C130" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D130" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E130" s="25" t="s">
+      <c r="D130" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E130" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F130" s="15" t="s">
@@ -6276,10 +6317,10 @@
       <c r="I130" s="16">
         <v>1431558165</v>
       </c>
-      <c r="J130" s="17">
+      <c r="J130" s="34">
         <v>96.06</v>
       </c>
-      <c r="K130" s="26" t="s">
+      <c r="K130" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -6287,48 +6328,48 @@
       <c r="A131" s="13">
         <v>65</v>
       </c>
-      <c r="B131" s="27" t="s">
+      <c r="B131" s="25" t="s">
         <v>216</v>
       </c>
       <c r="C131" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="D131" s="25">
+      <c r="D131" s="23">
         <v>46170</v>
       </c>
-      <c r="E131" s="25">
+      <c r="E131" s="23">
         <v>46178</v>
       </c>
-      <c r="F131" s="30" t="s">
+      <c r="F131" s="28" t="s">
         <v>218</v>
       </c>
       <c r="G131" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="H131" s="25" t="s">
+      <c r="H131" s="23" t="s">
         <v>219</v>
       </c>
       <c r="I131" s="16">
         <v>64750000</v>
       </c>
-      <c r="J131" s="17">
+      <c r="J131" s="34">
         <v>5.18</v>
       </c>
-      <c r="K131" s="26" t="s">
+      <c r="K131" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B132" s="27" t="s">
+      <c r="B132" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C132" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D132" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E132" s="25" t="s">
+      <c r="D132" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E132" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F132" s="15" t="s">
@@ -6343,10 +6384,10 @@
       <c r="I132" s="16">
         <v>582750000</v>
       </c>
-      <c r="J132" s="17">
+      <c r="J132" s="34">
         <v>5.18</v>
       </c>
-      <c r="K132" s="26" t="s">
+      <c r="K132" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -6354,48 +6395,48 @@
       <c r="A133" s="13">
         <v>66</v>
       </c>
-      <c r="B133" s="27" t="s">
+      <c r="B133" s="25" t="s">
         <v>220</v>
       </c>
       <c r="C133" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="D133" s="25">
+      <c r="D133" s="23">
         <v>46178</v>
       </c>
-      <c r="E133" s="25">
+      <c r="E133" s="23">
         <v>46188</v>
       </c>
-      <c r="F133" s="30" t="s">
+      <c r="F133" s="28" t="s">
         <v>222</v>
       </c>
       <c r="G133" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H133" s="25" t="s">
+      <c r="H133" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I133" s="16">
         <v>49964470</v>
       </c>
-      <c r="J133" s="17">
+      <c r="J133" s="34">
         <v>43.58</v>
       </c>
-      <c r="K133" s="26" t="s">
+      <c r="K133" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B134" s="27" t="s">
+      <c r="B134" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C134" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D134" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E134" s="25" t="s">
+      <c r="D134" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E134" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F134" s="15" t="s">
@@ -6410,10 +6451,10 @@
       <c r="I134" s="16">
         <v>449641008</v>
       </c>
-      <c r="J134" s="17">
+      <c r="J134" s="34">
         <v>43.58</v>
       </c>
-      <c r="K134" s="26" t="s">
+      <c r="K134" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -6421,48 +6462,48 @@
       <c r="A135" s="13">
         <v>67</v>
       </c>
-      <c r="B135" s="27" t="s">
+      <c r="B135" s="25" t="s">
         <v>223</v>
       </c>
       <c r="C135" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="D135" s="25">
+      <c r="D135" s="23">
         <v>46182</v>
       </c>
-      <c r="E135" s="25">
+      <c r="E135" s="23">
         <v>46190</v>
       </c>
-      <c r="F135" s="30" t="s">
+      <c r="F135" s="28" t="s">
         <v>225</v>
       </c>
       <c r="G135" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H135" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I135" s="31">
+      <c r="H135" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="I135" s="29">
         <v>98057088</v>
       </c>
-      <c r="J135" s="17">
+      <c r="J135" s="34">
         <v>18.36</v>
       </c>
-      <c r="K135" s="26" t="s">
+      <c r="K135" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B136" s="27" t="s">
+      <c r="B136" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C136" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D136" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E136" s="25" t="s">
+      <c r="D136" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E136" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F136" s="15" t="s">
@@ -6474,13 +6515,13 @@
       <c r="H136" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="I136" s="31">
+      <c r="I136" s="29">
         <v>934927920</v>
       </c>
-      <c r="J136" s="17">
+      <c r="J136" s="34">
         <v>18.36</v>
       </c>
-      <c r="K136" s="26" t="s">
+      <c r="K136" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -6488,48 +6529,48 @@
       <c r="A137" s="13">
         <v>68</v>
       </c>
-      <c r="B137" s="27" t="s">
+      <c r="B137" s="25" t="s">
         <v>226</v>
       </c>
       <c r="C137" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="D137" s="25">
+      <c r="D137" s="23">
         <v>46184</v>
       </c>
-      <c r="E137" s="25">
+      <c r="E137" s="23">
         <v>46195</v>
       </c>
-      <c r="F137" s="30" t="s">
+      <c r="F137" s="28" t="s">
         <v>228</v>
       </c>
       <c r="G137" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="H137" s="25" t="s">
+      <c r="H137" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I137" s="16">
         <v>61318800</v>
       </c>
-      <c r="J137" s="17">
+      <c r="J137" s="34">
         <v>7.2</v>
       </c>
-      <c r="K137" s="26" t="s">
+      <c r="K137" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B138" s="27" t="s">
+      <c r="B138" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C138" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D138" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E138" s="25" t="s">
+      <c r="D138" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E138" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F138" s="15" t="s">
@@ -6544,10 +6585,10 @@
       <c r="I138" s="16">
         <v>551851200</v>
       </c>
-      <c r="J138" s="17">
+      <c r="J138" s="34">
         <v>7.2</v>
       </c>
-      <c r="K138" s="26" t="s">
+      <c r="K138" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -6555,48 +6596,48 @@
       <c r="A139" s="13">
         <v>69</v>
       </c>
-      <c r="B139" s="27" t="s">
+      <c r="B139" s="25" t="s">
         <v>230</v>
       </c>
       <c r="C139" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="D139" s="25">
+      <c r="D139" s="23">
         <v>46185</v>
       </c>
-      <c r="E139" s="25">
+      <c r="E139" s="23">
         <v>46196</v>
       </c>
-      <c r="F139" s="30" t="s">
+      <c r="F139" s="28" t="s">
         <v>232</v>
       </c>
       <c r="G139" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="H139" s="25" t="s">
+      <c r="H139" s="23" t="s">
         <v>234</v>
       </c>
       <c r="I139" s="16">
         <v>134273450</v>
       </c>
-      <c r="J139" s="17">
+      <c r="J139" s="34">
         <v>8.98</v>
       </c>
-      <c r="K139" s="26" t="s">
+      <c r="K139" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B140" s="27" t="s">
+      <c r="B140" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C140" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D140" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E140" s="25" t="s">
+      <c r="D140" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E140" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F140" s="15" t="s">
@@ -6611,10 +6652,10 @@
       <c r="I140" s="16">
         <v>1208447580</v>
       </c>
-      <c r="J140" s="17">
+      <c r="J140" s="34">
         <v>8.98</v>
       </c>
-      <c r="K140" s="26" t="s">
+      <c r="K140" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -6622,48 +6663,48 @@
       <c r="A141" s="13">
         <v>70</v>
       </c>
-      <c r="B141" s="27" t="s">
+      <c r="B141" s="25" t="s">
         <v>235</v>
       </c>
       <c r="C141" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="D141" s="25">
+      <c r="D141" s="23">
         <v>46185</v>
       </c>
-      <c r="E141" s="25">
+      <c r="E141" s="23">
         <v>46196</v>
       </c>
-      <c r="F141" s="30" t="s">
+      <c r="F141" s="28" t="s">
         <v>117</v>
       </c>
       <c r="G141" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="H141" s="25" t="s">
+      <c r="H141" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I141" s="16">
         <v>111248000</v>
       </c>
-      <c r="J141" s="17">
+      <c r="J141" s="34">
         <v>81.8</v>
       </c>
-      <c r="K141" s="26" t="s">
+      <c r="K141" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B142" s="27" t="s">
+      <c r="B142" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C142" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D142" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E142" s="25" t="s">
+      <c r="D142" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E142" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F142" s="15" t="s">
@@ -6678,10 +6719,10 @@
       <c r="I142" s="16">
         <v>1001232000</v>
       </c>
-      <c r="J142" s="17">
+      <c r="J142" s="34">
         <v>81.8</v>
       </c>
-      <c r="K142" s="26" t="s">
+      <c r="K142" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -6689,48 +6730,48 @@
       <c r="A143" s="13">
         <v>71</v>
       </c>
-      <c r="B143" s="27" t="s">
+      <c r="B143" s="25" t="s">
         <v>238</v>
       </c>
       <c r="C143" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="D143" s="25">
+      <c r="D143" s="23">
         <v>46188</v>
       </c>
-      <c r="E143" s="25">
+      <c r="E143" s="23">
         <v>46197</v>
       </c>
-      <c r="F143" s="30" t="s">
+      <c r="F143" s="28" t="s">
         <v>240</v>
       </c>
       <c r="G143" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="H143" s="25" t="s">
+      <c r="H143" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I143" s="16">
         <v>105661920</v>
       </c>
-      <c r="J143" s="17">
+      <c r="J143" s="34">
         <v>18.2</v>
       </c>
-      <c r="K143" s="26" t="s">
+      <c r="K143" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B144" s="27" t="s">
+      <c r="B144" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C144" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D144" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E144" s="25" t="s">
+      <c r="D144" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E144" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F144" s="15" t="s">
@@ -6745,10 +6786,10 @@
       <c r="I144" s="16">
         <v>950928160</v>
       </c>
-      <c r="J144" s="17">
+      <c r="J144" s="34">
         <v>18.2</v>
       </c>
-      <c r="K144" s="26" t="s">
+      <c r="K144" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -6756,48 +6797,48 @@
       <c r="A145" s="13">
         <v>72</v>
       </c>
-      <c r="B145" s="27" t="s">
+      <c r="B145" s="25" t="s">
         <v>241</v>
       </c>
       <c r="C145" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="D145" s="25">
+      <c r="D145" s="23">
         <v>46188</v>
       </c>
-      <c r="E145" s="25">
+      <c r="E145" s="23">
         <v>46197</v>
       </c>
-      <c r="F145" s="30" t="s">
+      <c r="F145" s="28" t="s">
         <v>75</v>
       </c>
       <c r="G145" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H145" s="25" t="s">
+      <c r="H145" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I145" s="16">
         <v>213309200</v>
       </c>
-      <c r="J145" s="17">
+      <c r="J145" s="34">
         <v>101.6</v>
       </c>
-      <c r="K145" s="26" t="s">
+      <c r="K145" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B146" s="27" t="s">
+      <c r="B146" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C146" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D146" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E146" s="25" t="s">
+      <c r="D146" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E146" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F146" s="15" t="s">
@@ -6812,10 +6853,10 @@
       <c r="I146" s="16">
         <v>853216480</v>
       </c>
-      <c r="J146" s="17">
+      <c r="J146" s="34">
         <v>101.6</v>
       </c>
-      <c r="K146" s="26" t="s">
+      <c r="K146" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -6823,48 +6864,48 @@
       <c r="A147" s="13">
         <v>73</v>
       </c>
-      <c r="B147" s="27" t="s">
+      <c r="B147" s="25" t="s">
         <v>243</v>
       </c>
       <c r="C147" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="D147" s="25">
+      <c r="D147" s="23">
         <v>46190</v>
       </c>
-      <c r="E147" s="25">
+      <c r="E147" s="23">
         <v>46199</v>
       </c>
-      <c r="F147" s="30" t="s">
+      <c r="F147" s="28" t="s">
         <v>245</v>
       </c>
       <c r="G147" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="H147" s="25" t="s">
+      <c r="H147" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I147" s="16">
         <v>826425838</v>
       </c>
-      <c r="J147" s="17">
+      <c r="J147" s="34">
         <v>10.18</v>
       </c>
-      <c r="K147" s="26" t="s">
+      <c r="K147" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B148" s="27" t="s">
+      <c r="B148" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C148" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D148" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E148" s="25" t="s">
+      <c r="D148" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E148" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F148" s="15" t="s">
@@ -6879,10 +6920,10 @@
       <c r="I148" s="16">
         <v>7437819101</v>
       </c>
-      <c r="J148" s="17">
+      <c r="J148" s="34">
         <v>10.18</v>
       </c>
-      <c r="K148" s="26" t="s">
+      <c r="K148" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -6890,48 +6931,48 @@
       <c r="A149" s="13">
         <v>74</v>
       </c>
-      <c r="B149" s="27" t="s">
+      <c r="B149" s="25" t="s">
         <v>246</v>
       </c>
       <c r="C149" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="D149" s="25">
+      <c r="D149" s="23">
         <v>46190</v>
       </c>
-      <c r="E149" s="25">
+      <c r="E149" s="23">
         <v>46199</v>
       </c>
-      <c r="F149" s="30" t="s">
+      <c r="F149" s="28" t="s">
         <v>75</v>
       </c>
       <c r="G149" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H149" s="25" t="s">
+      <c r="H149" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I149" s="16">
         <v>180096900</v>
       </c>
-      <c r="J149" s="17">
+      <c r="J149" s="34">
         <v>60.7</v>
       </c>
-      <c r="K149" s="26" t="s">
+      <c r="K149" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B150" s="27" t="s">
+      <c r="B150" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C150" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D150" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E150" s="25" t="s">
+      <c r="D150" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E150" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F150" s="15" t="s">
@@ -6946,10 +6987,10 @@
       <c r="I150" s="16">
         <v>801397820</v>
       </c>
-      <c r="J150" s="17">
+      <c r="J150" s="34">
         <v>60.7</v>
       </c>
-      <c r="K150" s="26" t="s">
+      <c r="K150" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -6957,48 +6998,48 @@
       <c r="A151" s="13">
         <v>75</v>
       </c>
-      <c r="B151" s="27" t="s">
+      <c r="B151" s="25" t="s">
         <v>248</v>
       </c>
       <c r="C151" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="D151" s="25">
+      <c r="D151" s="23">
         <v>46190</v>
       </c>
-      <c r="E151" s="25">
+      <c r="E151" s="23">
         <v>46199</v>
       </c>
-      <c r="F151" s="30" t="s">
+      <c r="F151" s="28" t="s">
         <v>250</v>
       </c>
       <c r="G151" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H151" s="25" t="s">
+      <c r="H151" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I151" s="16">
         <v>39994542</v>
       </c>
-      <c r="J151" s="17">
+      <c r="J151" s="34">
         <v>39.549999999999997</v>
       </c>
-      <c r="K151" s="26" t="s">
+      <c r="K151" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B152" s="27" t="s">
+      <c r="B152" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C152" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D152" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E152" s="25" t="s">
+      <c r="D152" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E152" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F152" s="15" t="s">
@@ -7013,10 +7054,10 @@
       <c r="I152" s="16">
         <v>359946132</v>
       </c>
-      <c r="J152" s="17">
+      <c r="J152" s="34">
         <v>39.549999999999997</v>
       </c>
-      <c r="K152" s="26" t="s">
+      <c r="K152" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -7024,48 +7065,48 @@
       <c r="A153" s="13">
         <v>76</v>
       </c>
-      <c r="B153" s="27" t="s">
+      <c r="B153" s="25" t="s">
         <v>251</v>
       </c>
       <c r="C153" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="D153" s="25">
+      <c r="D153" s="23">
         <v>46190</v>
       </c>
-      <c r="E153" s="25">
+      <c r="E153" s="23">
         <v>46199</v>
       </c>
-      <c r="F153" s="30" t="s">
+      <c r="F153" s="28" t="s">
         <v>75</v>
       </c>
       <c r="G153" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H153" s="25" t="s">
+      <c r="H153" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I153" s="16">
         <v>324480047</v>
       </c>
-      <c r="J153" s="17">
+      <c r="J153" s="34">
         <v>252.73</v>
       </c>
-      <c r="K153" s="26" t="s">
+      <c r="K153" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B154" s="27" t="s">
+      <c r="B154" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C154" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D154" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E154" s="25" t="s">
+      <c r="D154" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E154" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F154" s="15" t="s">
@@ -7080,10 +7121,10 @@
       <c r="I154" s="16">
         <v>3406926765</v>
       </c>
-      <c r="J154" s="17">
+      <c r="J154" s="34">
         <v>252.73</v>
       </c>
-      <c r="K154" s="26" t="s">
+      <c r="K154" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -7091,48 +7132,48 @@
       <c r="A155" s="13">
         <v>77</v>
       </c>
-      <c r="B155" s="27" t="s">
+      <c r="B155" s="25" t="s">
         <v>253</v>
       </c>
       <c r="C155" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="D155" s="25">
+      <c r="D155" s="23">
         <v>46190</v>
       </c>
-      <c r="E155" s="25">
+      <c r="E155" s="23">
         <v>46199</v>
       </c>
-      <c r="F155" s="30" t="s">
+      <c r="F155" s="28" t="s">
         <v>255</v>
       </c>
       <c r="G155" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H155" s="25" t="s">
+      <c r="H155" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I155" s="16">
         <v>460097040</v>
       </c>
-      <c r="J155" s="17">
+      <c r="J155" s="34">
         <v>85.2</v>
       </c>
-      <c r="K155" s="26" t="s">
+      <c r="K155" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B156" s="27" t="s">
+      <c r="B156" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C156" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D156" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E156" s="25" t="s">
+      <c r="D156" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E156" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F156" s="15" t="s">
@@ -7147,10 +7188,10 @@
       <c r="I156" s="16">
         <v>4830933720</v>
       </c>
-      <c r="J156" s="17">
+      <c r="J156" s="34">
         <v>85.2</v>
       </c>
-      <c r="K156" s="26" t="s">
+      <c r="K156" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -7158,48 +7199,48 @@
       <c r="A157" s="13">
         <v>78</v>
       </c>
-      <c r="B157" s="27" t="s">
+      <c r="B157" s="25" t="s">
         <v>256</v>
       </c>
       <c r="C157" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="D157" s="25">
+      <c r="D157" s="23">
         <v>46190</v>
       </c>
-      <c r="E157" s="25">
+      <c r="E157" s="23">
         <v>46199</v>
       </c>
-      <c r="F157" s="30" t="s">
+      <c r="F157" s="28" t="s">
         <v>258</v>
       </c>
       <c r="G157" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="H157" s="25" t="s">
+      <c r="H157" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I157" s="16">
         <v>238519540</v>
       </c>
-      <c r="J157" s="17">
+      <c r="J157" s="34">
         <v>26.6</v>
       </c>
-      <c r="K157" s="26" t="s">
+      <c r="K157" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B158" s="27" t="s">
+      <c r="B158" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C158" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D158" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E158" s="25" t="s">
+      <c r="D158" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E158" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F158" s="15" t="s">
@@ -7214,10 +7255,10 @@
       <c r="I158" s="16">
         <v>2227502620</v>
       </c>
-      <c r="J158" s="17">
+      <c r="J158" s="34">
         <v>26.6</v>
       </c>
-      <c r="K158" s="26" t="s">
+      <c r="K158" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -7225,48 +7266,48 @@
       <c r="A159" s="13">
         <v>79</v>
       </c>
-      <c r="B159" s="27" t="s">
+      <c r="B159" s="25" t="s">
         <v>259</v>
       </c>
       <c r="C159" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="D159" s="25">
+      <c r="D159" s="23">
         <v>46191</v>
       </c>
-      <c r="E159" s="25">
+      <c r="E159" s="23">
         <v>46202</v>
       </c>
-      <c r="F159" s="30" t="s">
+      <c r="F159" s="28" t="s">
         <v>102</v>
       </c>
       <c r="G159" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H159" s="25" t="s">
+      <c r="H159" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I159" s="16">
         <v>153119100</v>
       </c>
-      <c r="J159" s="17">
+      <c r="J159" s="34">
         <v>114</v>
       </c>
-      <c r="K159" s="26" t="s">
+      <c r="K159" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B160" s="27" t="s">
+      <c r="B160" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C160" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D160" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E160" s="25" t="s">
+      <c r="D160" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E160" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F160" s="15" t="s">
@@ -7281,10 +7322,10 @@
       <c r="I160" s="16">
         <v>1607747700</v>
       </c>
-      <c r="J160" s="17">
+      <c r="J160" s="34">
         <v>114</v>
       </c>
-      <c r="K160" s="26" t="s">
+      <c r="K160" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -7292,48 +7333,48 @@
       <c r="A161" s="13">
         <v>80</v>
       </c>
-      <c r="B161" s="27" t="s">
+      <c r="B161" s="25" t="s">
         <v>261</v>
       </c>
       <c r="C161" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="D161" s="25">
+      <c r="D161" s="23">
         <v>46191</v>
       </c>
-      <c r="E161" s="25">
+      <c r="E161" s="23">
         <v>46202</v>
       </c>
-      <c r="F161" s="30" t="s">
+      <c r="F161" s="28" t="s">
         <v>263</v>
       </c>
       <c r="G161" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="H161" s="25" t="s">
+      <c r="H161" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I161" s="16">
         <v>52019760</v>
       </c>
-      <c r="J161" s="17">
+      <c r="J161" s="34">
         <v>15.6</v>
       </c>
-      <c r="K161" s="26" t="s">
+      <c r="K161" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B162" s="27" t="s">
+      <c r="B162" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C162" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D162" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E162" s="25" t="s">
+      <c r="D162" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E162" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F162" s="15" t="s">
@@ -7348,10 +7389,10 @@
       <c r="I162" s="16">
         <v>468152880</v>
       </c>
-      <c r="J162" s="17">
+      <c r="J162" s="34">
         <v>15.6</v>
       </c>
-      <c r="K162" s="26" t="s">
+      <c r="K162" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -7359,48 +7400,48 @@
       <c r="A163" s="13">
         <v>81</v>
       </c>
-      <c r="B163" s="27" t="s">
+      <c r="B163" s="25" t="s">
         <v>265</v>
       </c>
       <c r="C163" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="D163" s="25">
+      <c r="D163" s="23">
         <v>46191</v>
       </c>
-      <c r="E163" s="25">
+      <c r="E163" s="23">
         <v>46202</v>
       </c>
-      <c r="F163" s="30" t="s">
+      <c r="F163" s="28" t="s">
         <v>267</v>
       </c>
       <c r="G163" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H163" s="25" t="s">
+      <c r="H163" s="23" t="s">
         <v>13</v>
       </c>
       <c r="I163" s="16">
         <v>128268560</v>
       </c>
-      <c r="J163" s="17">
+      <c r="J163" s="34">
         <v>22.6</v>
       </c>
-      <c r="K163" s="26" t="s">
+      <c r="K163" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B164" s="27" t="s">
+      <c r="B164" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C164" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D164" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E164" s="25" t="s">
+      <c r="D164" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E164" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F164" s="15" t="s">
@@ -7415,10 +7456,10 @@
       <c r="I164" s="16">
         <v>1346804060</v>
       </c>
-      <c r="J164" s="17">
+      <c r="J164" s="34">
         <v>22.6</v>
       </c>
-      <c r="K164" s="26" t="s">
+      <c r="K164" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -7426,48 +7467,48 @@
       <c r="A165" s="13">
         <v>82</v>
       </c>
-      <c r="B165" s="27" t="s">
+      <c r="B165" s="25" t="s">
         <v>268</v>
       </c>
       <c r="C165" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="D165" s="25">
+      <c r="D165" s="23">
         <v>46195</v>
       </c>
-      <c r="E165" s="25">
+      <c r="E165" s="23">
         <v>46203</v>
       </c>
-      <c r="F165" s="30" t="s">
+      <c r="F165" s="28" t="s">
         <v>270</v>
       </c>
       <c r="G165" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H165" s="25" t="s">
+      <c r="H165" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I165" s="16">
         <v>44987776</v>
       </c>
-      <c r="J165" s="17">
+      <c r="J165" s="34">
         <v>126.2</v>
       </c>
-      <c r="K165" s="26" t="s">
+      <c r="K165" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B166" s="27" t="s">
+      <c r="B166" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C166" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D166" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E166" s="25" t="s">
+      <c r="D166" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E166" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F166" s="15" t="s">
@@ -7482,10 +7523,10 @@
       <c r="I166" s="16">
         <v>404877364</v>
       </c>
-      <c r="J166" s="17">
+      <c r="J166" s="34">
         <v>126.2</v>
       </c>
-      <c r="K166" s="26" t="s">
+      <c r="K166" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -7493,48 +7534,48 @@
       <c r="A167" s="13">
         <v>83</v>
       </c>
-      <c r="B167" s="27" t="s">
+      <c r="B167" s="25" t="s">
         <v>271</v>
       </c>
       <c r="C167" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="D167" s="25">
+      <c r="D167" s="23">
         <v>46195</v>
       </c>
-      <c r="E167" s="25">
+      <c r="E167" s="23">
         <v>46203</v>
       </c>
-      <c r="F167" s="30" t="s">
+      <c r="F167" s="28" t="s">
         <v>273</v>
       </c>
       <c r="G167" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="H167" s="25" t="s">
+      <c r="H167" s="23" t="s">
         <v>72</v>
       </c>
       <c r="I167" s="16">
         <v>40583200</v>
       </c>
-      <c r="J167" s="17">
+      <c r="J167" s="34">
         <v>11.2</v>
       </c>
-      <c r="K167" s="26" t="s">
+      <c r="K167" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B168" s="27" t="s">
+      <c r="B168" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C168" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D168" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E168" s="25" t="s">
+      <c r="D168" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E168" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F168" s="15" t="s">
@@ -7549,10 +7590,10 @@
       <c r="I168" s="16">
         <v>365243200</v>
       </c>
-      <c r="J168" s="17">
+      <c r="J168" s="34">
         <v>11.2</v>
       </c>
-      <c r="K168" s="26" t="s">
+      <c r="K168" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -7560,48 +7601,48 @@
       <c r="A169" s="13">
         <v>84</v>
       </c>
-      <c r="B169" s="27" t="s">
+      <c r="B169" s="25" t="s">
         <v>274</v>
       </c>
       <c r="C169" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="D169" s="25">
+      <c r="D169" s="23">
         <v>46195</v>
       </c>
-      <c r="E169" s="25">
+      <c r="E169" s="23">
         <v>46203</v>
       </c>
-      <c r="F169" s="30" t="s">
+      <c r="F169" s="28" t="s">
         <v>276</v>
       </c>
       <c r="G169" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H169" s="25" t="s">
+      <c r="H169" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I169" s="16">
         <v>229858200</v>
       </c>
-      <c r="J169" s="17">
+      <c r="J169" s="34">
         <v>85.5</v>
       </c>
-      <c r="K169" s="26" t="s">
+      <c r="K169" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B170" s="27" t="s">
+      <c r="B170" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C170" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D170" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E170" s="25" t="s">
+      <c r="D170" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E170" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F170" s="15" t="s">
@@ -7616,10 +7657,10 @@
       <c r="I170" s="16">
         <v>982386450</v>
       </c>
-      <c r="J170" s="17">
+      <c r="J170" s="34">
         <v>85.5</v>
       </c>
-      <c r="K170" s="26" t="s">
+      <c r="K170" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -7627,48 +7668,48 @@
       <c r="A171" s="13">
         <v>85</v>
       </c>
-      <c r="B171" s="27" t="s">
+      <c r="B171" s="25" t="s">
         <v>277</v>
       </c>
       <c r="C171" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="D171" s="25">
+      <c r="D171" s="23">
         <v>46195</v>
       </c>
-      <c r="E171" s="25">
+      <c r="E171" s="23">
         <v>46203</v>
       </c>
-      <c r="F171" s="30" t="s">
+      <c r="F171" s="28" t="s">
         <v>279</v>
       </c>
       <c r="G171" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="H171" s="25" t="s">
+      <c r="H171" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I171" s="16">
         <v>123314150</v>
       </c>
-      <c r="J171" s="17">
+      <c r="J171" s="34">
         <v>75.5</v>
       </c>
-      <c r="K171" s="26" t="s">
+      <c r="K171" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B172" s="27" t="s">
+      <c r="B172" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C172" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D172" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E172" s="25" t="s">
+      <c r="D172" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E172" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F172" s="15" t="s">
@@ -7683,10 +7724,10 @@
       <c r="I172" s="16">
         <v>1109819800</v>
       </c>
-      <c r="J172" s="17">
+      <c r="J172" s="34">
         <v>75.5</v>
       </c>
-      <c r="K172" s="26" t="s">
+      <c r="K172" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -7694,48 +7735,48 @@
       <c r="A173" s="13">
         <v>86</v>
       </c>
-      <c r="B173" s="27" t="s">
+      <c r="B173" s="25" t="s">
         <v>280</v>
       </c>
-      <c r="C173" s="32" t="s">
+      <c r="C173" s="30" t="s">
         <v>281</v>
       </c>
-      <c r="D173" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="E173" s="25">
+      <c r="D173" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E173" s="23">
         <v>46203</v>
       </c>
-      <c r="F173" s="25" t="s">
+      <c r="F173" s="23" t="s">
         <v>21</v>
       </c>
       <c r="G173" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="H173" s="25" t="s">
+      <c r="H173" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I173" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="J173" s="17" t="s">
+      <c r="J173" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="K173" s="26" t="s">
+      <c r="K173" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="174" spans="1:11" ht="45" x14ac:dyDescent="0.2">
-      <c r="B174" s="27" t="s">
+      <c r="B174" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C174" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D174" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E174" s="25" t="s">
+      <c r="D174" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E174" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F174" s="15" t="s">
@@ -7750,10 +7791,10 @@
       <c r="I174" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="J174" s="17" t="s">
+      <c r="J174" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="K174" s="26" t="s">
+      <c r="K174" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -7761,48 +7802,48 @@
       <c r="A175" s="13">
         <v>87</v>
       </c>
-      <c r="B175" s="27" t="s">
+      <c r="B175" s="25" t="s">
         <v>283</v>
       </c>
       <c r="C175" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="D175" s="25">
+      <c r="D175" s="23">
         <v>46196</v>
       </c>
-      <c r="E175" s="25">
+      <c r="E175" s="23">
         <v>46205</v>
       </c>
-      <c r="F175" s="30" t="s">
+      <c r="F175" s="28" t="s">
         <v>285</v>
       </c>
       <c r="G175" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H175" s="25" t="s">
+      <c r="H175" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I175" s="16">
         <v>463158956</v>
       </c>
-      <c r="J175" s="17">
+      <c r="J175" s="34">
         <v>99.32</v>
       </c>
-      <c r="K175" s="26" t="s">
+      <c r="K175" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B176" s="27" t="s">
+      <c r="B176" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C176" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D176" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E176" s="25" t="s">
+      <c r="D176" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E176" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F176" s="15" t="s">
@@ -7817,10 +7858,10 @@
       <c r="I176" s="16">
         <v>4510399296</v>
       </c>
-      <c r="J176" s="17">
+      <c r="J176" s="34">
         <v>99.32</v>
       </c>
-      <c r="K176" s="26" t="s">
+      <c r="K176" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -7828,48 +7869,48 @@
       <c r="A177" s="13">
         <v>88</v>
       </c>
-      <c r="B177" s="27" t="s">
+      <c r="B177" s="25" t="s">
         <v>286</v>
       </c>
       <c r="C177" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="D177" s="25">
+      <c r="D177" s="23">
         <v>46199</v>
       </c>
-      <c r="E177" s="25">
+      <c r="E177" s="23">
         <v>46210</v>
       </c>
-      <c r="F177" s="30" t="s">
+      <c r="F177" s="28" t="s">
         <v>75</v>
       </c>
       <c r="G177" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H177" s="25" t="s">
+      <c r="H177" s="23" t="s">
         <v>72</v>
       </c>
       <c r="I177" s="16">
         <v>59485250</v>
       </c>
-      <c r="J177" s="17">
+      <c r="J177" s="34">
         <v>5.5</v>
       </c>
-      <c r="K177" s="26" t="s">
+      <c r="K177" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B178" s="27" t="s">
+      <c r="B178" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C178" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D178" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E178" s="25" t="s">
+      <c r="D178" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E178" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F178" s="15" t="s">
@@ -7884,10 +7925,10 @@
       <c r="I178" s="16">
         <v>535359000</v>
       </c>
-      <c r="J178" s="17">
+      <c r="J178" s="34">
         <v>5.5</v>
       </c>
-      <c r="K178" s="26" t="s">
+      <c r="K178" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -7895,48 +7936,48 @@
       <c r="A179" s="13">
         <v>89</v>
       </c>
-      <c r="B179" s="27" t="s">
+      <c r="B179" s="25" t="s">
         <v>288</v>
       </c>
       <c r="C179" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="D179" s="25">
+      <c r="D179" s="23">
         <v>46202</v>
       </c>
-      <c r="E179" s="25">
+      <c r="E179" s="23">
         <v>46211</v>
       </c>
-      <c r="F179" s="30" t="s">
+      <c r="F179" s="28" t="s">
         <v>290</v>
       </c>
       <c r="G179" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H179" s="25" t="s">
+      <c r="H179" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I179" s="16">
         <v>121672884</v>
       </c>
-      <c r="J179" s="17">
+      <c r="J179" s="34">
         <v>21.66</v>
       </c>
-      <c r="K179" s="26" t="s">
+      <c r="K179" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B180" s="27" t="s">
+      <c r="B180" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C180" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D180" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E180" s="25" t="s">
+      <c r="D180" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E180" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F180" s="15" t="s">
@@ -7951,10 +7992,10 @@
       <c r="I180" s="16">
         <v>486691536</v>
       </c>
-      <c r="J180" s="17">
+      <c r="J180" s="34">
         <v>21.66</v>
       </c>
-      <c r="K180" s="26" t="s">
+      <c r="K180" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -7962,48 +8003,48 @@
       <c r="A181" s="13">
         <v>90</v>
       </c>
-      <c r="B181" s="27" t="s">
+      <c r="B181" s="25" t="s">
         <v>291</v>
       </c>
       <c r="C181" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="D181" s="25">
+      <c r="D181" s="23">
         <v>46202</v>
       </c>
-      <c r="E181" s="25">
+      <c r="E181" s="23">
         <v>46211</v>
       </c>
-      <c r="F181" s="30" t="s">
+      <c r="F181" s="28" t="s">
         <v>293</v>
       </c>
       <c r="G181" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H181" s="25" t="s">
+      <c r="H181" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I181" s="16">
         <v>173195388</v>
       </c>
-      <c r="J181" s="17">
+      <c r="J181" s="34">
         <v>31.62</v>
       </c>
-      <c r="K181" s="26" t="s">
+      <c r="K181" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B182" s="27" t="s">
+      <c r="B182" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C182" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D182" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E182" s="25" t="s">
+      <c r="D182" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E182" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F182" s="15" t="s">
@@ -8018,10 +8059,10 @@
       <c r="I182" s="16">
         <v>692756256</v>
       </c>
-      <c r="J182" s="17">
+      <c r="J182" s="34">
         <v>31.62</v>
       </c>
-      <c r="K182" s="26" t="s">
+      <c r="K182" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -8029,48 +8070,48 @@
       <c r="A183" s="13">
         <v>91</v>
       </c>
-      <c r="B183" s="27" t="s">
+      <c r="B183" s="25" t="s">
         <v>294</v>
       </c>
-      <c r="C183" s="32" t="s">
+      <c r="C183" s="30" t="s">
         <v>295</v>
       </c>
-      <c r="D183" s="25">
+      <c r="D183" s="23">
         <v>46202</v>
       </c>
-      <c r="E183" s="25">
+      <c r="E183" s="23">
         <v>46211</v>
       </c>
-      <c r="F183" s="30" t="s">
+      <c r="F183" s="28" t="s">
         <v>296</v>
       </c>
       <c r="G183" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="H183" s="25" t="s">
+      <c r="H183" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I183" s="16">
         <v>589379104</v>
       </c>
-      <c r="J183" s="17">
+      <c r="J183" s="34">
         <v>295.60000000000002</v>
       </c>
-      <c r="K183" s="26" t="s">
+      <c r="K183" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B184" s="27" t="s">
+      <c r="B184" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C184" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D184" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E184" s="25" t="s">
+      <c r="D184" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E184" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F184" s="15" t="s">
@@ -8085,10 +8126,10 @@
       <c r="I184" s="16">
         <v>5304382376</v>
       </c>
-      <c r="J184" s="17">
+      <c r="J184" s="34">
         <v>295.60000000000002</v>
       </c>
-      <c r="K184" s="26" t="s">
+      <c r="K184" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -8096,48 +8137,48 @@
       <c r="A185" s="13">
         <v>92</v>
       </c>
-      <c r="B185" s="27" t="s">
+      <c r="B185" s="25" t="s">
         <v>297</v>
       </c>
-      <c r="C185" s="32" t="s">
+      <c r="C185" s="30" t="s">
         <v>298</v>
       </c>
-      <c r="D185" s="25">
+      <c r="D185" s="23">
         <v>46202</v>
       </c>
-      <c r="E185" s="25">
+      <c r="E185" s="23">
         <v>46211</v>
       </c>
-      <c r="F185" s="30" t="s">
+      <c r="F185" s="28" t="s">
         <v>299</v>
       </c>
       <c r="G185" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="H185" s="25" t="s">
+      <c r="H185" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I185" s="16">
         <v>229752544</v>
       </c>
-      <c r="J185" s="17">
+      <c r="J185" s="34">
         <v>87.92</v>
       </c>
-      <c r="K185" s="26" t="s">
+      <c r="K185" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B186" s="27" t="s">
+      <c r="B186" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C186" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D186" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E186" s="25" t="s">
+      <c r="D186" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E186" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F186" s="15" t="s">
@@ -8152,10 +8193,10 @@
       <c r="I186" s="16">
         <v>2311403612</v>
       </c>
-      <c r="J186" s="17">
+      <c r="J186" s="34">
         <v>87.92</v>
       </c>
-      <c r="K186" s="26" t="s">
+      <c r="K186" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -8163,48 +8204,48 @@
       <c r="A187" s="13">
         <v>93</v>
       </c>
-      <c r="B187" s="27" t="s">
+      <c r="B187" s="25" t="s">
         <v>300</v>
       </c>
-      <c r="C187" s="32" t="s">
+      <c r="C187" s="30" t="s">
         <v>301</v>
       </c>
-      <c r="D187" s="25">
+      <c r="D187" s="23">
         <v>46202</v>
       </c>
-      <c r="E187" s="25">
+      <c r="E187" s="23">
         <v>46212</v>
       </c>
-      <c r="F187" s="30" t="s">
+      <c r="F187" s="28" t="s">
         <v>117</v>
       </c>
       <c r="G187" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="H187" s="25" t="s">
+      <c r="H187" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I187" s="16">
         <v>40255816</v>
       </c>
-      <c r="J187" s="17">
+      <c r="J187" s="34">
         <v>78.64</v>
       </c>
-      <c r="K187" s="26" t="s">
+      <c r="K187" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B188" s="27" t="s">
+      <c r="B188" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C188" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D188" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E188" s="25" t="s">
+      <c r="D188" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E188" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F188" s="15" t="s">
@@ -8219,10 +8260,10 @@
       <c r="I188" s="16">
         <v>362270888</v>
       </c>
-      <c r="J188" s="17">
+      <c r="J188" s="34">
         <v>78.64</v>
       </c>
-      <c r="K188" s="26" t="s">
+      <c r="K188" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -8230,48 +8271,48 @@
       <c r="A189" s="13">
         <v>94</v>
       </c>
-      <c r="B189" s="27" t="s">
+      <c r="B189" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="C189" s="32" t="s">
+      <c r="C189" s="30" t="s">
         <v>304</v>
       </c>
-      <c r="D189" s="25">
+      <c r="D189" s="23">
         <v>46203</v>
       </c>
-      <c r="E189" s="25">
+      <c r="E189" s="23">
         <v>46212</v>
       </c>
-      <c r="F189" s="30" t="s">
+      <c r="F189" s="28" t="s">
         <v>117</v>
       </c>
       <c r="G189" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="H189" s="25" t="s">
+      <c r="H189" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I189" s="16">
         <v>114044194</v>
       </c>
-      <c r="J189" s="17">
+      <c r="J189" s="34">
         <v>45.98</v>
       </c>
-      <c r="K189" s="26" t="s">
+      <c r="K189" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B190" s="27" t="s">
+      <c r="B190" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C190" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D190" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E190" s="25" t="s">
+      <c r="D190" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E190" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F190" s="15" t="s">
@@ -8286,10 +8327,10 @@
       <c r="I190" s="16">
         <v>1026360962</v>
       </c>
-      <c r="J190" s="17">
+      <c r="J190" s="34">
         <v>45.98</v>
       </c>
-      <c r="K190" s="26" t="s">
+      <c r="K190" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -8297,48 +8338,48 @@
       <c r="A191" s="13">
         <v>95</v>
       </c>
-      <c r="B191" s="27" t="s">
+      <c r="B191" s="25" t="s">
         <v>305</v>
       </c>
-      <c r="C191" s="32" t="s">
+      <c r="C191" s="30" t="s">
         <v>306</v>
       </c>
-      <c r="D191" s="25">
+      <c r="D191" s="23">
         <v>46203</v>
       </c>
-      <c r="E191" s="25">
+      <c r="E191" s="23">
         <v>46212</v>
       </c>
-      <c r="F191" s="30" t="s">
+      <c r="F191" s="28" t="s">
         <v>307</v>
       </c>
       <c r="G191" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="H191" s="25" t="s">
+      <c r="H191" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I191" s="16">
         <v>480016000</v>
       </c>
-      <c r="J191" s="17">
+      <c r="J191" s="34">
         <v>380</v>
       </c>
-      <c r="K191" s="26" t="s">
+      <c r="K191" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B192" s="27" t="s">
+      <c r="B192" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C192" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D192" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E192" s="25" t="s">
+      <c r="D192" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E192" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F192" s="15" t="s">
@@ -8353,10 +8394,10 @@
       <c r="I192" s="16">
         <v>4320144000</v>
       </c>
-      <c r="J192" s="17">
+      <c r="J192" s="34">
         <v>380</v>
       </c>
-      <c r="K192" s="26" t="s">
+      <c r="K192" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -8364,48 +8405,48 @@
       <c r="A193" s="13">
         <v>96</v>
       </c>
-      <c r="B193" s="27" t="s">
+      <c r="B193" s="25" t="s">
         <v>308</v>
       </c>
-      <c r="C193" s="32" t="s">
+      <c r="C193" s="30" t="s">
         <v>309</v>
       </c>
-      <c r="D193" s="25">
+      <c r="D193" s="23">
         <v>46203</v>
       </c>
-      <c r="E193" s="25">
+      <c r="E193" s="23">
         <v>46212</v>
       </c>
-      <c r="F193" s="30" t="s">
+      <c r="F193" s="28" t="s">
         <v>310</v>
       </c>
       <c r="G193" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="H193" s="25" t="s">
+      <c r="H193" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I193" s="16">
         <v>2426617144</v>
       </c>
-      <c r="J193" s="17">
+      <c r="J193" s="34">
         <v>63.28</v>
       </c>
-      <c r="K193" s="26" t="s">
+      <c r="K193" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="194" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B194" s="27" t="s">
+      <c r="B194" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C194" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D194" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E194" s="25" t="s">
+      <c r="D194" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E194" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F194" s="15" t="s">
@@ -8420,10 +8461,10 @@
       <c r="I194" s="16">
         <v>22633193072</v>
       </c>
-      <c r="J194" s="17">
+      <c r="J194" s="34">
         <v>63.28</v>
       </c>
-      <c r="K194" s="26" t="s">
+      <c r="K194" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -8431,48 +8472,48 @@
       <c r="A195" s="13">
         <v>97</v>
       </c>
-      <c r="B195" s="27" t="s">
+      <c r="B195" s="25" t="s">
         <v>312</v>
       </c>
-      <c r="C195" s="32" t="s">
+      <c r="C195" s="30" t="s">
         <v>313</v>
       </c>
-      <c r="D195" s="25">
+      <c r="D195" s="23">
         <v>46203</v>
       </c>
-      <c r="E195" s="25">
+      <c r="E195" s="23">
         <v>46212</v>
       </c>
-      <c r="F195" s="30" t="s">
+      <c r="F195" s="28" t="s">
         <v>314</v>
       </c>
       <c r="G195" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="H195" s="25" t="s">
+      <c r="H195" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I195" s="16">
         <v>87521600</v>
       </c>
-      <c r="J195" s="17">
+      <c r="J195" s="34">
         <v>38</v>
       </c>
-      <c r="K195" s="26" t="s">
+      <c r="K195" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="196" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B196" s="27" t="s">
+      <c r="B196" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C196" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D196" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E196" s="25" t="s">
+      <c r="D196" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E196" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F196" s="15" t="s">
@@ -8487,10 +8528,10 @@
       <c r="I196" s="16">
         <v>918969200</v>
       </c>
-      <c r="J196" s="17">
+      <c r="J196" s="34">
         <v>38</v>
       </c>
-      <c r="K196" s="26" t="s">
+      <c r="K196" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -8498,48 +8539,48 @@
       <c r="A197" s="13">
         <v>98</v>
       </c>
-      <c r="B197" s="27" t="s">
+      <c r="B197" s="25" t="s">
         <v>315</v>
       </c>
-      <c r="C197" s="32" t="s">
+      <c r="C197" s="30" t="s">
         <v>316</v>
       </c>
-      <c r="D197" s="25">
+      <c r="D197" s="23">
         <v>46203</v>
       </c>
-      <c r="E197" s="25">
+      <c r="E197" s="23">
         <v>46212</v>
       </c>
-      <c r="F197" s="30" t="s">
+      <c r="F197" s="28" t="s">
         <v>317</v>
       </c>
       <c r="G197" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="H197" s="25" t="s">
+      <c r="H197" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I197" s="16">
         <v>715790950</v>
       </c>
-      <c r="J197" s="17">
+      <c r="J197" s="34">
         <v>100.3</v>
       </c>
-      <c r="K197" s="26" t="s">
+      <c r="K197" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="198" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B198" s="27" t="s">
+      <c r="B198" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C198" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D198" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E198" s="25" t="s">
+      <c r="D198" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E198" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F198" s="15" t="s">
@@ -8554,10 +8595,10 @@
       <c r="I198" s="16">
         <v>7330395410</v>
       </c>
-      <c r="J198" s="17">
+      <c r="J198" s="34">
         <v>100.3</v>
       </c>
-      <c r="K198" s="26" t="s">
+      <c r="K198" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -8565,19 +8606,19 @@
       <c r="A199" s="13">
         <v>99</v>
       </c>
-      <c r="B199" s="27" t="s">
+      <c r="B199" s="25" t="s">
         <v>318</v>
       </c>
       <c r="C199" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="D199" s="25">
+      <c r="D199" s="23">
         <v>46203</v>
       </c>
-      <c r="E199" s="25">
+      <c r="E199" s="23">
         <v>46212</v>
       </c>
-      <c r="F199" s="30" t="s">
+      <c r="F199" s="28" t="s">
         <v>320</v>
       </c>
       <c r="G199" s="15" t="s">
@@ -8589,24 +8630,24 @@
       <c r="I199" s="16">
         <v>20000000</v>
       </c>
-      <c r="J199" s="17">
+      <c r="J199" s="34">
         <v>8</v>
       </c>
-      <c r="K199" s="26" t="s">
+      <c r="K199" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="200" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B200" s="27" t="s">
+      <c r="B200" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C200" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D200" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E200" s="25" t="s">
+      <c r="D200" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E200" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F200" s="15" t="s">
@@ -8621,10 +8662,10 @@
       <c r="I200" s="16">
         <v>180000000</v>
       </c>
-      <c r="J200" s="17">
+      <c r="J200" s="34">
         <v>8</v>
       </c>
-      <c r="K200" s="26" t="s">
+      <c r="K200" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -8632,34 +8673,34 @@
       <c r="A201" s="13">
         <v>100</v>
       </c>
-      <c r="B201" s="27" t="s">
+      <c r="B201" s="25" t="s">
         <v>322</v>
       </c>
       <c r="C201" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="D201" s="25">
+      <c r="D201" s="23">
         <v>46203</v>
       </c>
-      <c r="E201" s="25">
+      <c r="E201" s="23">
         <v>46213</v>
       </c>
-      <c r="F201" s="30" t="s">
+      <c r="F201" s="28" t="s">
         <v>75</v>
       </c>
       <c r="G201" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="H201" s="25" t="s">
+      <c r="H201" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I201" s="16">
         <v>698219410</v>
       </c>
-      <c r="J201" s="17">
+      <c r="J201" s="34">
         <v>32.299999999999997</v>
       </c>
-      <c r="K201" s="26" t="s">
+      <c r="K201" s="24" t="s">
         <v>14</v>
       </c>
       <c r="L201" s="13"/>
@@ -8668,16 +8709,16 @@
       <c r="O201" s="13"/>
     </row>
     <row r="202" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B202" s="27" t="s">
+      <c r="B202" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C202" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D202" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E202" s="25" t="s">
+      <c r="D202" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E202" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F202" s="15" t="s">
@@ -8692,49 +8733,49 @@
       <c r="I202" s="16">
         <v>6635621560</v>
       </c>
-      <c r="J202" s="17">
+      <c r="J202" s="34">
         <v>32.299999999999997</v>
       </c>
-      <c r="K202" s="26" t="s">
+      <c r="K202" s="24" t="s">
         <v>16</v>
       </c>
       <c r="L202" s="13"/>
       <c r="M202" s="13"/>
       <c r="N202" s="13"/>
-      <c r="O202" s="33"/>
+      <c r="O202" s="31"/>
     </row>
     <row r="203" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A203" s="13">
         <v>101</v>
       </c>
-      <c r="B203" s="27" t="s">
+      <c r="B203" s="25" t="s">
         <v>324</v>
       </c>
       <c r="C203" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="D203" s="25">
+      <c r="D203" s="23">
         <v>46203</v>
       </c>
-      <c r="E203" s="25">
+      <c r="E203" s="23">
         <v>46213</v>
       </c>
-      <c r="F203" s="30" t="s">
+      <c r="F203" s="28" t="s">
         <v>326</v>
       </c>
       <c r="G203" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H203" s="25" t="s">
+      <c r="H203" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I203" s="16">
         <v>122541240</v>
       </c>
-      <c r="J203" s="17">
+      <c r="J203" s="34">
         <v>3.48</v>
       </c>
-      <c r="K203" s="26" t="s">
+      <c r="K203" s="24" t="s">
         <v>14</v>
       </c>
       <c r="L203" s="13"/>
@@ -8743,16 +8784,16 @@
       <c r="O203" s="13"/>
     </row>
     <row r="204" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B204" s="27" t="s">
+      <c r="B204" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C204" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D204" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E204" s="25" t="s">
+      <c r="D204" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E204" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F204" s="15" t="s">
@@ -8767,49 +8808,49 @@
       <c r="I204" s="16">
         <v>1102857240</v>
       </c>
-      <c r="J204" s="17">
+      <c r="J204" s="34">
         <v>3.48</v>
       </c>
-      <c r="K204" s="26" t="s">
+      <c r="K204" s="24" t="s">
         <v>16</v>
       </c>
       <c r="L204" s="13"/>
       <c r="M204" s="13"/>
       <c r="N204" s="13"/>
-      <c r="O204" s="33"/>
+      <c r="O204" s="31"/>
     </row>
     <row r="205" spans="1:15" ht="75" x14ac:dyDescent="0.2">
       <c r="A205" s="13">
         <v>102</v>
       </c>
-      <c r="B205" s="27" t="s">
+      <c r="B205" s="25" t="s">
         <v>327</v>
       </c>
       <c r="C205" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="D205" s="25">
+      <c r="D205" s="23">
         <v>46225</v>
       </c>
-      <c r="E205" s="25">
+      <c r="E205" s="23">
         <v>46233</v>
       </c>
-      <c r="F205" s="30" t="s">
+      <c r="F205" s="28" t="s">
         <v>329</v>
       </c>
       <c r="G205" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="H205" s="25" t="s">
+      <c r="H205" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I205" s="16">
         <v>5341000000</v>
       </c>
-      <c r="J205" s="17">
+      <c r="J205" s="34">
         <v>980</v>
       </c>
-      <c r="K205" s="26" t="s">
+      <c r="K205" s="24" t="s">
         <v>14</v>
       </c>
       <c r="L205" s="13"/>
@@ -8818,16 +8859,16 @@
       <c r="O205" s="13"/>
     </row>
     <row r="206" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B206" s="27" t="s">
+      <c r="B206" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C206" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D206" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E206" s="25" t="s">
+      <c r="D206" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E206" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F206" s="15" t="s">
@@ -8842,49 +8883,49 @@
       <c r="I206" s="16">
         <v>56080500000</v>
       </c>
-      <c r="J206" s="17">
+      <c r="J206" s="34">
         <v>980</v>
       </c>
-      <c r="K206" s="26" t="s">
+      <c r="K206" s="24" t="s">
         <v>16</v>
       </c>
       <c r="L206" s="13"/>
       <c r="M206" s="13"/>
       <c r="N206" s="13"/>
-      <c r="O206" s="33"/>
+      <c r="O206" s="31"/>
     </row>
     <row r="207" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A207" s="13">
         <v>103</v>
       </c>
-      <c r="B207" s="27" t="s">
+      <c r="B207" s="25" t="s">
         <v>330</v>
       </c>
       <c r="C207" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="D207" s="25">
+      <c r="D207" s="23">
         <v>46233</v>
       </c>
-      <c r="E207" s="25">
+      <c r="E207" s="23">
         <v>46241</v>
       </c>
-      <c r="F207" s="30" t="s">
+      <c r="F207" s="28" t="s">
         <v>332</v>
       </c>
       <c r="G207" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H207" s="25" t="s">
+      <c r="H207" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I207" s="16">
         <v>60013990</v>
       </c>
-      <c r="J207" s="17">
+      <c r="J207" s="34">
         <v>10.42</v>
       </c>
-      <c r="K207" s="26" t="s">
+      <c r="K207" s="24" t="s">
         <v>14</v>
       </c>
       <c r="L207" s="13"/>
@@ -8893,16 +8934,16 @@
       <c r="O207" s="13"/>
     </row>
     <row r="208" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B208" s="27" t="s">
+      <c r="B208" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C208" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D208" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E208" s="25" t="s">
+      <c r="D208" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E208" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F208" s="15" t="s">
@@ -8917,49 +8958,49 @@
       <c r="I208" s="16">
         <v>540120700</v>
       </c>
-      <c r="J208" s="17">
+      <c r="J208" s="34">
         <v>10.42</v>
       </c>
-      <c r="K208" s="26" t="s">
+      <c r="K208" s="24" t="s">
         <v>16</v>
       </c>
       <c r="L208" s="13"/>
       <c r="M208" s="13"/>
       <c r="N208" s="13"/>
-      <c r="O208" s="33"/>
+      <c r="O208" s="31"/>
     </row>
     <row r="209" spans="1:15" ht="30" x14ac:dyDescent="0.2">
       <c r="A209" s="13">
         <v>104</v>
       </c>
-      <c r="B209" s="27" t="s">
+      <c r="B209" s="25" t="s">
         <v>333</v>
       </c>
       <c r="C209" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="D209" s="25">
+      <c r="D209" s="23">
         <v>46251</v>
       </c>
-      <c r="E209" s="25">
+      <c r="E209" s="23">
         <v>46259</v>
       </c>
-      <c r="F209" s="30" t="s">
+      <c r="F209" s="28" t="s">
         <v>245</v>
       </c>
       <c r="G209" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="H209" s="25" t="s">
+      <c r="H209" s="23" t="s">
         <v>21</v>
       </c>
       <c r="I209" s="16">
         <v>312880000</v>
       </c>
-      <c r="J209" s="17">
+      <c r="J209" s="34">
         <v>100</v>
       </c>
-      <c r="K209" s="26" t="s">
+      <c r="K209" s="24" t="s">
         <v>14</v>
       </c>
       <c r="L209" s="13"/>
@@ -8968,16 +9009,16 @@
       <c r="O209" s="13"/>
     </row>
     <row r="210" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B210" s="27" t="s">
+      <c r="B210" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C210" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D210" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E210" s="25" t="s">
+      <c r="D210" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E210" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F210" s="15" t="s">
@@ -8992,31 +9033,31 @@
       <c r="I210" s="16">
         <v>2815850000</v>
       </c>
-      <c r="J210" s="17">
+      <c r="J210" s="34">
         <v>100</v>
       </c>
-      <c r="K210" s="26" t="s">
+      <c r="K210" s="24" t="s">
         <v>16</v>
       </c>
       <c r="L210" s="13"/>
       <c r="M210" s="13"/>
       <c r="N210" s="13"/>
-      <c r="O210" s="33"/>
+      <c r="O210" s="31"/>
     </row>
     <row r="211" spans="1:15" ht="45" x14ac:dyDescent="0.2">
       <c r="A211" s="13">
         <v>105</v>
       </c>
-      <c r="B211" s="27" t="s">
+      <c r="B211" s="25" t="s">
         <v>335</v>
       </c>
       <c r="C211" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="D211" s="25">
+      <c r="D211" s="23">
         <v>46258</v>
       </c>
-      <c r="E211" s="25">
+      <c r="E211" s="23">
         <v>46266</v>
       </c>
       <c r="F211" s="15" t="s">
@@ -9031,28 +9072,28 @@
       <c r="I211" s="16">
         <v>470680821</v>
       </c>
-      <c r="J211" s="17">
+      <c r="J211" s="34">
         <v>101.7</v>
       </c>
-      <c r="K211" s="26" t="s">
+      <c r="K211" s="24" t="s">
         <v>14</v>
       </c>
       <c r="L211" s="13"/>
       <c r="M211" s="13"/>
       <c r="N211" s="13"/>
-      <c r="O211" s="33"/>
+      <c r="O211" s="31"/>
     </row>
     <row r="212" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B212" s="27" t="s">
+      <c r="B212" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C212" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D212" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E212" s="25" t="s">
+      <c r="D212" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E212" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F212" s="15" t="s">
@@ -9067,10 +9108,10 @@
       <c r="I212" s="16">
         <v>1882717182</v>
       </c>
-      <c r="J212" s="17">
+      <c r="J212" s="34">
         <v>101.7</v>
       </c>
-      <c r="K212" s="26" t="s">
+      <c r="K212" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -9078,16 +9119,16 @@
       <c r="A213" s="13">
         <v>106</v>
       </c>
-      <c r="B213" s="27" t="s">
+      <c r="B213" s="25" t="s">
         <v>338</v>
       </c>
       <c r="C213" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="D213" s="25">
+      <c r="D213" s="23">
         <v>46258</v>
       </c>
-      <c r="E213" s="25">
+      <c r="E213" s="23">
         <v>46266</v>
       </c>
       <c r="F213" s="15" t="s">
@@ -9102,24 +9143,24 @@
       <c r="I213" s="16">
         <v>1359646008</v>
       </c>
-      <c r="J213" s="17">
+      <c r="J213" s="34">
         <v>48.56</v>
       </c>
-      <c r="K213" s="26" t="s">
+      <c r="K213" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="214" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B214" s="27" t="s">
+      <c r="B214" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C214" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D214" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E214" s="25" t="s">
+      <c r="D214" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E214" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F214" s="15" t="s">
@@ -9134,10 +9175,10 @@
       <c r="I214" s="16">
         <v>12236789792</v>
       </c>
-      <c r="J214" s="17">
+      <c r="J214" s="34">
         <v>48.56</v>
       </c>
-      <c r="K214" s="26" t="s">
+      <c r="K214" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -9145,16 +9186,16 @@
       <c r="A215" s="13">
         <v>107</v>
       </c>
-      <c r="B215" s="27" t="s">
+      <c r="B215" s="25" t="s">
         <v>345</v>
       </c>
       <c r="C215" s="14" t="s">
         <v>346</v>
       </c>
-      <c r="D215" s="25">
+      <c r="D215" s="23">
         <v>46262</v>
       </c>
-      <c r="E215" s="25">
+      <c r="E215" s="23">
         <v>46272</v>
       </c>
       <c r="F215" s="15" t="s">
@@ -9169,24 +9210,24 @@
       <c r="I215" s="16">
         <v>60000762</v>
       </c>
-      <c r="J215" s="17">
+      <c r="J215" s="34">
         <v>15.42</v>
       </c>
-      <c r="K215" s="26" t="s">
+      <c r="K215" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="216" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B216" s="27" t="s">
+      <c r="B216" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C216" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D216" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E216" s="25" t="s">
+      <c r="D216" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E216" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F216" s="15" t="s">
@@ -9201,10 +9242,10 @@
       <c r="I216" s="16">
         <v>540000690</v>
       </c>
-      <c r="J216" s="17">
+      <c r="J216" s="34">
         <v>15.42</v>
       </c>
-      <c r="K216" s="26" t="s">
+      <c r="K216" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -9212,16 +9253,16 @@
       <c r="A217" s="13">
         <v>108</v>
       </c>
-      <c r="B217" s="27" t="s">
+      <c r="B217" s="25" t="s">
         <v>348</v>
       </c>
       <c r="C217" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="D217" s="25">
+      <c r="D217" s="23">
         <v>46265</v>
       </c>
-      <c r="E217" s="25">
+      <c r="E217" s="23">
         <v>46273</v>
       </c>
       <c r="F217" s="15" t="s">
@@ -9236,24 +9277,24 @@
       <c r="I217" s="16">
         <v>615440800</v>
       </c>
-      <c r="J217" s="17">
+      <c r="J217" s="34">
         <v>236</v>
       </c>
-      <c r="K217" s="26" t="s">
+      <c r="K217" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="218" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B218" s="27" t="s">
+      <c r="B218" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C218" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D218" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E218" s="25" t="s">
+      <c r="D218" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E218" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F218" s="15" t="s">
@@ -9268,10 +9309,10 @@
       <c r="I218" s="16">
         <v>6462069400</v>
       </c>
-      <c r="J218" s="17">
+      <c r="J218" s="34">
         <v>236</v>
       </c>
-      <c r="K218" s="26" t="s">
+      <c r="K218" s="24" t="s">
         <v>16</v>
       </c>
     </row>
@@ -9279,20 +9320,20 @@
       <c r="A219" s="13">
         <v>109</v>
       </c>
-      <c r="B219" s="27" t="s">
+      <c r="B219" s="25" t="s">
+        <v>351</v>
+      </c>
+      <c r="C219" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="C219" s="14" t="s">
+      <c r="D219" s="23">
+        <v>46265</v>
+      </c>
+      <c r="E219" s="23">
+        <v>46274</v>
+      </c>
+      <c r="F219" s="15" t="s">
         <v>353</v>
-      </c>
-      <c r="D219" s="25">
-        <v>46265</v>
-      </c>
-      <c r="E219" s="25">
-        <v>46274</v>
-      </c>
-      <c r="F219" s="15" t="s">
-        <v>354</v>
       </c>
       <c r="G219" s="15" t="s">
         <v>25</v>
@@ -9303,24 +9344,24 @@
       <c r="I219" s="16">
         <v>40197010</v>
       </c>
-      <c r="J219" s="17">
+      <c r="J219" s="34">
         <v>14.45</v>
       </c>
-      <c r="K219" s="26" t="s">
+      <c r="K219" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="220" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B220" s="27" t="s">
+      <c r="B220" s="25" t="s">
         <v>15</v>
       </c>
       <c r="C220" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D220" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E220" s="25" t="s">
+      <c r="D220" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E220" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F220" s="15" t="s">
@@ -9335,41 +9376,501 @@
       <c r="I220" s="16">
         <v>610052990</v>
       </c>
-      <c r="J220" s="17">
+      <c r="J220" s="34">
         <v>14.45</v>
       </c>
-      <c r="K220" s="26" t="s">
+      <c r="K220" s="24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="221" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B221" s="27"/>
-      <c r="D221" s="25"/>
-      <c r="E221" s="25"/>
-      <c r="F221" s="15"/>
-      <c r="G221" s="15"/>
-      <c r="H221" s="15"/>
-      <c r="I221" s="16"/>
+      <c r="A221" s="13">
+        <v>110</v>
+      </c>
+      <c r="B221" s="25">
+        <v>6727</v>
+      </c>
+      <c r="C221" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="D221" s="23">
+        <v>46276</v>
+      </c>
+      <c r="E221" s="23">
+        <v>46286</v>
+      </c>
+      <c r="F221" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="G221" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="H221" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I221" s="16">
+        <f>J221*2802200</f>
+        <v>137307800</v>
+      </c>
+      <c r="J221" s="35">
+        <v>49</v>
+      </c>
+      <c r="K221" s="24" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="222" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C222" s="23" t="s">
+      <c r="B222" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C222" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D222" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E222" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F222" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G222" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H222" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I222" s="16">
+        <f>J222*11208600</f>
+        <v>549221400</v>
+      </c>
+      <c r="J222" s="35">
+        <v>49</v>
+      </c>
+      <c r="K222" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="223" spans="1:15" ht="30" x14ac:dyDescent="0.2">
+      <c r="A223" s="13">
+        <v>111</v>
+      </c>
+      <c r="B223" s="25">
+        <v>9856</v>
+      </c>
+      <c r="C223" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="D223" s="23">
+        <v>46279</v>
+      </c>
+      <c r="E223" s="23">
+        <v>46287</v>
+      </c>
+      <c r="F223" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="G223" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H223" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I223" s="16">
+        <f>17201500*J223</f>
+        <v>566961440</v>
+      </c>
+      <c r="J223" s="35">
+        <v>32.96</v>
+      </c>
+      <c r="K223" s="24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B224" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C224" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D224" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E224" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F224" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G224" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H224" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I224" s="16">
+        <f>154813200*J224</f>
+        <v>5102643072</v>
+      </c>
+      <c r="J224" s="35">
+        <v>32.96</v>
+      </c>
+      <c r="K224" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A225" s="13">
+        <v>112</v>
+      </c>
+      <c r="B225" s="25">
+        <v>6731</v>
+      </c>
+      <c r="C225" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="D225" s="23">
+        <v>46286</v>
+      </c>
+      <c r="E225" s="23">
+        <v>46294</v>
+      </c>
+      <c r="F225" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G225" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H225" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I225" s="16">
+        <f>10000000*J225</f>
+        <v>216000000</v>
+      </c>
+      <c r="J225" s="35">
+        <v>21.6</v>
+      </c>
+      <c r="K225" s="24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B226" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C226" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D226" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E226" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F226" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G226" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H226" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I226" s="16">
+        <f>40000000*J226</f>
+        <v>864000000</v>
+      </c>
+      <c r="J226" s="35">
+        <v>21.6</v>
+      </c>
+      <c r="K226" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A227" s="13">
+        <v>113</v>
+      </c>
+      <c r="B227" s="25">
+        <v>9607</v>
+      </c>
+      <c r="C227" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="D227" s="23">
+        <v>46286</v>
+      </c>
+      <c r="E227" s="23">
+        <v>46294</v>
+      </c>
+      <c r="F227" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="G227" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H227" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I227" s="16">
+        <f>6811900*J227</f>
+        <v>299723600</v>
+      </c>
+      <c r="J227" s="35">
+        <v>44</v>
+      </c>
+      <c r="K227" s="24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B228" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C228" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D228" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E228" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F228" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G228" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H228" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I228" s="16">
+        <f>61306800*J228</f>
+        <v>2697499200</v>
+      </c>
+      <c r="J228" s="35">
+        <v>44</v>
+      </c>
+      <c r="K228" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" ht="45" x14ac:dyDescent="0.2">
+      <c r="A229" s="13">
+        <v>114</v>
+      </c>
+      <c r="B229" s="25">
+        <v>3757</v>
+      </c>
+      <c r="C229" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="D229" s="23">
+        <v>46286</v>
+      </c>
+      <c r="E229" s="23">
+        <v>46294</v>
+      </c>
+      <c r="F229" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="G229" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="H229" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I229" s="16">
+        <f>J229*1187600</f>
+        <v>517793600</v>
+      </c>
+      <c r="J229" s="35">
+        <v>436</v>
+      </c>
+      <c r="K229" s="24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B230" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C230" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D230" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E230" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F230" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G230" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H230" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I230" s="16">
+        <f>J230*10688400</f>
+        <v>4660142400</v>
+      </c>
+      <c r="J230" s="35">
+        <v>436</v>
+      </c>
+      <c r="K230" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" ht="60" x14ac:dyDescent="0.2">
+      <c r="A231" s="13">
+        <v>115</v>
+      </c>
+      <c r="B231" s="25">
+        <v>3228</v>
+      </c>
+      <c r="C231" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="D231" s="23">
+        <v>46286</v>
+      </c>
+      <c r="E231" s="23">
+        <v>46294</v>
+      </c>
+      <c r="F231" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="G231" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H231" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I231" s="16">
+        <f>7294500*J231</f>
+        <v>509739659.99999994</v>
+      </c>
+      <c r="J231" s="35">
+        <v>69.88</v>
+      </c>
+      <c r="K231" s="24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B232" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C232" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D232" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E232" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F232" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G232" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H232" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I232" s="16">
+        <f>65649800*J232</f>
+        <v>4587608024</v>
+      </c>
+      <c r="J232" s="35">
+        <v>69.88</v>
+      </c>
+      <c r="K232" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B233" s="25"/>
+      <c r="D233" s="23"/>
+      <c r="E233" s="23"/>
+      <c r="F233" s="4"/>
+      <c r="G233" s="4"/>
+      <c r="H233" s="15"/>
+      <c r="I233" s="16"/>
+      <c r="K233" s="24"/>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B234" s="25"/>
+      <c r="D234" s="23"/>
+      <c r="E234" s="23"/>
+      <c r="F234" s="15"/>
+      <c r="G234" s="15"/>
+      <c r="H234" s="15"/>
+      <c r="I234" s="16"/>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B235" s="25"/>
+      <c r="D235" s="23"/>
+      <c r="E235" s="23"/>
+      <c r="F235" s="15"/>
+      <c r="G235" s="15"/>
+      <c r="H235" s="15"/>
+      <c r="I235" s="16"/>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B236" s="25"/>
+      <c r="D236" s="23"/>
+      <c r="E236" s="23"/>
+      <c r="F236" s="15"/>
+      <c r="G236" s="15"/>
+      <c r="H236" s="15"/>
+      <c r="I236" s="16"/>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B237" s="25"/>
+      <c r="D237" s="23"/>
+      <c r="E237" s="23"/>
+      <c r="F237" s="15"/>
+      <c r="G237" s="15"/>
+      <c r="H237" s="15"/>
+      <c r="I237" s="16"/>
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B238" s="25"/>
+      <c r="D238" s="23"/>
+      <c r="E238" s="23"/>
+      <c r="F238" s="15"/>
+      <c r="G238" s="15"/>
+      <c r="H238" s="15"/>
+      <c r="I238" s="16"/>
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C239" s="21" t="s">
         <v>341</v>
       </c>
-      <c r="H222" s="20"/>
-    </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C223" s="23" t="s">
+      <c r="H239" s="19"/>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="C240" s="21" t="s">
         <v>342</v>
       </c>
-      <c r="H223" s="20"/>
-    </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C224" s="14" t="s">
+      <c r="H240" s="19"/>
+    </row>
+    <row r="241" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C241" s="14" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="225" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C225" s="23" t="s">
+    <row r="242" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C242" s="21" t="s">
         <v>344</v>
       </c>
     </row>
@@ -9386,6 +9887,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="3583b915-8c05-47e0-b602-6b944e48abf6" xsi:nil="true"/>
@@ -9396,7 +9906,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000955781E8111C0408E1513F95C30BCFD" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2689884b2ccf74a0e750e03ecad47a8a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="925dd3d5-7c0d-4068-9ad5-72245214adae" xmlns:ns3="3583b915-8c05-47e0-b602-6b944e48abf6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="484ded3d5d35b5d9dcd2efbfa69676e4" ns2:_="" ns3:_="">
     <xsd:import namespace="925dd3d5-7c0d-4068-9ad5-72245214adae"/>
@@ -9603,16 +10113,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C21CF38F-26C0-4B0D-87AB-B90D6385230C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{509311FB-C656-467C-B5B0-DA8A169DF54E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -9629,7 +10138,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1C1E9C1-E47A-45C8-B9D7-C2172BF7FEAC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9646,12 +10155,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C21CF38F-26C0-4B0D-87AB-B90D6385230C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>